--- a/source/APPN/TD_APPN_Common_v2.xlsx
+++ b/source/APPN/TD_APPN_Common_v2.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,6 +21,8 @@
     <sheet name="Deployment" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="GrowthFacility" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="GrowthFacilityType" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="PhysicalContainmentLevel" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="BiocontainmentLevel" sheetId="15" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Trait!$L$1:$L$78</definedName>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="256">
   <si>
     <t xml:space="preserve">APPN Adelaide University vocabularies</t>
   </si>
@@ -1376,6 +1378,71 @@
   <si>
     <t xml:space="preserve">A cohort is a collection of material entities grouped together based on some common property of interest, such as age or disease stage</t>
   </si>
+  <si>
+    <t xml:space="preserve">PC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Containment Level 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A facility certified as a PC 1 Facility is appropriate for the conduct of the dealings listed below, provided it meets the specific requirements described in the PC 1 Facility guidelines for the dealing type:
+- GM micro-organisms (when there is less than or equal to 25 litres of culture of any one GMO);
+- GM animals (whether or not they contain microorganisms) as permitted by the Gene Technology Regulations 2001;
+- non GM animals containing GM micro-organisms; and
+- non-GM plants that contain or host GMOs.
+A PC 1 Facility is not appropriate for the following:
+- dealings with any GMO that under the Act, or under the conditions of a licence, requires containment in any PC level higher than PC 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Containment Level 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A facility certified as a PC 2 Plant Facility is appropriate for the conduct of the dealings listed below:
+- the growing of GM terrestrial plants; or
+- the growing of terrestrial plants that contain GMOs.
+A PC 2 Plant Facility is not appropriate for the following:
+- dealings with any GMO that under the conditions of a licence or legislation requires containment in any PC level higher than PC 2;
+- the housing/keeping/rearing of any animals, invertebrates, or aquatic organisms unless they are integral to the dealing being contained in the facility;
+- dealings producing more than 25 litres of liquid culture of GMOs in each vessel; or
+- any other work prohibited in writing by the Regulator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Containment Level 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A facility certified as a PC 3 Facility is appropriate for the conduct of the dealings listed below:
+- dealings with GM micro-organisms;
+- laboratory procedures involving small terrestrial animals and invertebrates, if not otherwise prohibited by licence conditions;
+- laboratory procedures involving aquatic organisms (including amphibians), subject to additional conditions and if not otherwise prohibited by licence conditions.
+A PC 3 Facility is not appropriate for the following:
+- dealings with any GMO that, under the gene technology legislation or conditions of a licence, require containment in a physical containment level higher than PC3;
+- dealings involving a micro-organism that satisfies the criteria in AS/NZS 2243.3 for classification as Risk Group 4;
+- the housing/keeping/rearing of any plants, animals, including invertebrates and aquatic organisms, beyond the minimum time that they are required for conducting the dealings with GMOs; or
+- any other work prohibited by notification in writing by the Regulator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Containment Level 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A facility certified as a PC 4 Facility is appropriate for the conduct of dealings that are authorised by a licence requiring this level of containment This generally involves organisms classified as Risk group 4, or Risk group 3 (RG3) organisms which have been modified and as a result are more harmful than the RG3 parent organism. Dealings permitted to be conducted
+within the facility are therefore the result of an extensive risk assessment of proposed projects and the mandatory implementation of a risk management plan through licence conditions.
+The Guidelines contains the requirement for certification of a PC 4 Facility to be certified, and the conditions a facility must continue to comply for the facility to remain certified. Given the type of dealings conducted within the facility and the characteristics of the facility, bespoke requirements and conditions are likely to be included in the certification instrument.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC5.2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biosecurity containment level for plant material</t>
+  </si>
 </sst>
 </file>
 
@@ -1386,7 +1453,7 @@
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0%"/>
   </numFmts>
-  <fonts count="49">
+  <fonts count="48">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1433,14 +1500,6 @@
     </font>
     <font>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1585,12 +1644,6 @@
       <name val="Aptos Narrow"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="0"/>
     </font>
     <font>
       <u val="single"/>
@@ -1742,6 +1795,12 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="0"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -1759,7 +1818,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDEDCE6"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
     <fill>
@@ -2175,7 +2234,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2183,1033 +2242,1053 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="262">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="21" fillId="8" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="9" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="9" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="10" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="10" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="11" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="11" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="9" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="9" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="12" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="5" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="13" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="14" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="14" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="15" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="16" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="17" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="17" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="19" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="21" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="21" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="21" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="21" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="23" fillId="21" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="21" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="21" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="22" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="22" fillId="22" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="21" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="23" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="23" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="18" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="18" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="18" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="24" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="26" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="26" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="26" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="27" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="27" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="28" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="28" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="28" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="28" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="28" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="28" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="28" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="28" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="29" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="30" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="30" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="30" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="30" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="31" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="31" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="31" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="32" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="23" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="23" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="23" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="23" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="23" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="14" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="14" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="14" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="14" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="14" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="14" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="14" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="18" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="18" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="18" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="40" fillId="24" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="24" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="25" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="25" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="26" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="26" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="26" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="26" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="26" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="27" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="27" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="43" fillId="27" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="28" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="28" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="28" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="28" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="28" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="28" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="28" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="44" fillId="28" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="29" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="30" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="30" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="30" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="30" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="47" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="31" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="31" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="31" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="31" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="32" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="48" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="32" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="32" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="46" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="47" fillId="33" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3289,7 +3368,7 @@
       <rgbColor rgb="FFDEE7E5"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FFF2E4F1"/>
+      <rgbColor rgb="FFDEDCE6"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FFDAE9F8"/>
@@ -3310,10 +3389,10 @@
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF50938A"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFF2E5F1"/>
       <rgbColor rgb="FFC9211E"/>
-      <rgbColor rgb="FFDEDCE6"/>
-      <rgbColor rgb="FFF2E5F1"/>
+      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FFF2E4F1"/>
       <rgbColor rgb="FF292929"/>
     </indexedColors>
   </colors>
@@ -3529,13 +3608,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3565,7 +3644,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3580,7 +3659,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3590,7 +3669,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3600,15 +3679,15 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3618,44 +3697,44 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8"/>
+      <c r="A42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8"/>
+      <c r="A43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8"/>
+      <c r="A46" s="7"/>
     </row>
     <row r="47" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8"/>
+      <c r="A49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3679,155 +3758,155 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="117" width="28.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="117" width="52.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="117" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="114" width="28.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="114" width="52.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="114" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="126" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="160" t="s">
+    <row r="1" s="123" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="157" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="161" t="s">
+      <c r="B1" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="161" t="s">
+      <c r="C1" s="158" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="159" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="163"/>
-      <c r="C2" s="164" t="s">
+      <c r="B2" s="160"/>
+      <c r="C2" s="161" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="165" t="s">
+      <c r="A3" s="162" t="s">
         <v>198</v>
       </c>
-      <c r="B3" s="166"/>
-      <c r="C3" s="164" t="s">
+      <c r="B3" s="163"/>
+      <c r="C3" s="161" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="167" t="s">
+      <c r="A4" s="164" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="163"/>
-      <c r="C4" s="164" t="s">
+      <c r="B4" s="160"/>
+      <c r="C4" s="161" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="168" t="s">
+      <c r="A5" s="165" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="166"/>
-      <c r="C5" s="164" t="s">
+      <c r="B5" s="163"/>
+      <c r="C5" s="161" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="169" t="s">
+      <c r="A6" s="166" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="170"/>
-      <c r="C6" s="171" t="s">
+      <c r="B6" s="167"/>
+      <c r="C6" s="168" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="172" t="s">
+      <c r="A7" s="169" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="172"/>
-      <c r="C7" s="173" t="s">
+      <c r="B7" s="169"/>
+      <c r="C7" s="170" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="174"/>
-      <c r="B8" s="174"/>
-      <c r="C8" s="174"/>
+      <c r="A8" s="171"/>
+      <c r="B8" s="171"/>
+      <c r="C8" s="171"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="174"/>
-      <c r="B9" s="174"/>
-      <c r="C9" s="174"/>
+      <c r="A9" s="171"/>
+      <c r="B9" s="171"/>
+      <c r="C9" s="171"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="174"/>
-      <c r="B10" s="174"/>
-      <c r="C10" s="174"/>
+      <c r="A10" s="171"/>
+      <c r="B10" s="171"/>
+      <c r="C10" s="171"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="174"/>
-      <c r="B11" s="174"/>
-      <c r="C11" s="174"/>
+      <c r="A11" s="171"/>
+      <c r="B11" s="171"/>
+      <c r="C11" s="171"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="174"/>
-      <c r="B12" s="174"/>
-      <c r="C12" s="174"/>
+      <c r="A12" s="171"/>
+      <c r="B12" s="171"/>
+      <c r="C12" s="171"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="174"/>
-      <c r="B13" s="174"/>
-      <c r="C13" s="174"/>
+      <c r="A13" s="171"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="171"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="174"/>
-      <c r="B14" s="174"/>
-      <c r="C14" s="174"/>
+      <c r="A14" s="171"/>
+      <c r="B14" s="171"/>
+      <c r="C14" s="171"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="174"/>
-      <c r="B15" s="174"/>
-      <c r="C15" s="174"/>
+      <c r="A15" s="171"/>
+      <c r="B15" s="171"/>
+      <c r="C15" s="171"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="174"/>
-      <c r="B16" s="174"/>
-      <c r="C16" s="174"/>
+      <c r="A16" s="171"/>
+      <c r="B16" s="171"/>
+      <c r="C16" s="171"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="174"/>
-      <c r="B17" s="174"/>
-      <c r="C17" s="174"/>
+      <c r="A17" s="171"/>
+      <c r="B17" s="171"/>
+      <c r="C17" s="171"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="174"/>
-      <c r="B18" s="174"/>
-      <c r="C18" s="174"/>
+      <c r="A18" s="171"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="171"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="174"/>
-      <c r="B19" s="174"/>
-      <c r="C19" s="174"/>
+      <c r="A19" s="171"/>
+      <c r="B19" s="171"/>
+      <c r="C19" s="171"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="174"/>
-      <c r="B20" s="174"/>
-      <c r="C20" s="174"/>
+      <c r="A20" s="171"/>
+      <c r="B20" s="171"/>
+      <c r="C20" s="171"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="174"/>
-      <c r="B21" s="174"/>
-      <c r="C21" s="174"/>
+      <c r="A21" s="171"/>
+      <c r="B21" s="171"/>
+      <c r="C21" s="171"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="174"/>
-      <c r="B22" s="174"/>
-      <c r="C22" s="174"/>
+      <c r="A22" s="171"/>
+      <c r="B22" s="171"/>
+      <c r="C22" s="171"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="174"/>
-      <c r="B23" s="174"/>
-      <c r="C23" s="174"/>
+      <c r="A23" s="171"/>
+      <c r="B23" s="171"/>
+      <c r="C23" s="171"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3849,141 +3928,141 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="172" width="32.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="172" width="46.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="172" width="52.63"/>
   </cols>
   <sheetData>
-    <row r="1" s="178" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="175" t="s">
+    <row r="1" s="176" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="173" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="176" t="s">
+      <c r="B1" s="174" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="177" t="s">
+      <c r="C1" s="175" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="179"/>
-      <c r="B2" s="180"/>
-      <c r="C2" s="181"/>
+      <c r="A2" s="177"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="179"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="182"/>
-      <c r="B3" s="183"/>
-      <c r="C3" s="184"/>
+      <c r="A3" s="180"/>
+      <c r="B3" s="181"/>
+      <c r="C3" s="182"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="185"/>
-      <c r="B4" s="186"/>
-      <c r="C4" s="184"/>
+      <c r="A4" s="183"/>
+      <c r="B4" s="184"/>
+      <c r="C4" s="182"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="187"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="187"/>
+      <c r="A5" s="185"/>
+      <c r="B5" s="185"/>
+      <c r="C5" s="185"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="187"/>
-      <c r="B6" s="187"/>
-      <c r="C6" s="187"/>
+      <c r="A6" s="185"/>
+      <c r="B6" s="185"/>
+      <c r="C6" s="185"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="187"/>
-      <c r="B7" s="187"/>
-      <c r="C7" s="187"/>
+      <c r="A7" s="185"/>
+      <c r="B7" s="185"/>
+      <c r="C7" s="185"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="187"/>
-      <c r="B8" s="187"/>
-      <c r="C8" s="187"/>
+      <c r="A8" s="185"/>
+      <c r="B8" s="185"/>
+      <c r="C8" s="185"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="187"/>
-      <c r="B9" s="187"/>
-      <c r="C9" s="187"/>
+      <c r="A9" s="185"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="187"/>
-      <c r="B10" s="187"/>
-      <c r="C10" s="187"/>
+      <c r="A10" s="185"/>
+      <c r="B10" s="185"/>
+      <c r="C10" s="185"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="187"/>
-      <c r="B11" s="187"/>
-      <c r="C11" s="187"/>
+      <c r="A11" s="185"/>
+      <c r="B11" s="185"/>
+      <c r="C11" s="185"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="187"/>
-      <c r="B12" s="187"/>
-      <c r="C12" s="187"/>
+      <c r="A12" s="185"/>
+      <c r="B12" s="185"/>
+      <c r="C12" s="185"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="187"/>
-      <c r="B13" s="187"/>
-      <c r="C13" s="187"/>
+      <c r="A13" s="185"/>
+      <c r="B13" s="185"/>
+      <c r="C13" s="185"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="187"/>
-      <c r="B14" s="187"/>
-      <c r="C14" s="187"/>
+      <c r="A14" s="185"/>
+      <c r="B14" s="185"/>
+      <c r="C14" s="185"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="187"/>
-      <c r="B15" s="187"/>
-      <c r="C15" s="187"/>
+      <c r="A15" s="185"/>
+      <c r="B15" s="185"/>
+      <c r="C15" s="185"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="187"/>
-      <c r="B16" s="187"/>
-      <c r="C16" s="187"/>
+      <c r="A16" s="185"/>
+      <c r="B16" s="185"/>
+      <c r="C16" s="185"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="187"/>
-      <c r="B17" s="187"/>
-      <c r="C17" s="187"/>
+      <c r="A17" s="185"/>
+      <c r="B17" s="185"/>
+      <c r="C17" s="185"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="187"/>
-      <c r="B18" s="187"/>
-      <c r="C18" s="187"/>
+      <c r="A18" s="185"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="187"/>
-      <c r="B19" s="187"/>
-      <c r="C19" s="187"/>
+      <c r="A19" s="185"/>
+      <c r="B19" s="185"/>
+      <c r="C19" s="185"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="187"/>
-      <c r="B20" s="187"/>
-      <c r="C20" s="187"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="185"/>
+      <c r="C20" s="185"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="187"/>
-      <c r="B21" s="187"/>
-      <c r="C21" s="187"/>
+      <c r="A21" s="185"/>
+      <c r="B21" s="185"/>
+      <c r="C21" s="185"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="187"/>
-      <c r="B22" s="187"/>
-      <c r="C22" s="187"/>
+      <c r="A22" s="185"/>
+      <c r="B22" s="185"/>
+      <c r="C22" s="185"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="187"/>
-      <c r="B23" s="187"/>
-      <c r="C23" s="187"/>
+      <c r="A23" s="185"/>
+      <c r="B23" s="185"/>
+      <c r="C23" s="185"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="187"/>
-      <c r="B24" s="187"/>
-      <c r="C24" s="187"/>
+      <c r="A24" s="185"/>
+      <c r="B24" s="185"/>
+      <c r="C24" s="185"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="187"/>
-      <c r="B25" s="187"/>
-      <c r="C25" s="187"/>
+      <c r="A25" s="185"/>
+      <c r="B25" s="185"/>
+      <c r="C25" s="185"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4005,1211 +4084,1211 @@
   <dimension ref="A1:Q61"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="42.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="32.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="33.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="26.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="172" width="23.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="172" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="172" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="172" width="25.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="172" width="35.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="172" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="172" width="23.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="172" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="172" width="26.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="172" width="20.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="172" width="42.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="172" width="32.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="172" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="172" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="172" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="172" width="26.63"/>
   </cols>
   <sheetData>
-    <row r="1" s="73" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="188" t="s">
+    <row r="1" s="70" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="186" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="189" t="s">
+      <c r="B1" s="187" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="190" t="s">
+      <c r="C1" s="188" t="s">
         <v>208</v>
       </c>
-      <c r="D1" s="191" t="s">
+      <c r="D1" s="189" t="s">
         <v>209</v>
       </c>
-      <c r="E1" s="192" t="s">
+      <c r="E1" s="190" t="s">
         <v>210</v>
       </c>
-      <c r="F1" s="193" t="s">
+      <c r="F1" s="191" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="192" t="s">
+      <c r="G1" s="190" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="191" t="s">
+      <c r="H1" s="189" t="s">
         <v>213</v>
       </c>
-      <c r="I1" s="194" t="s">
+      <c r="I1" s="192" t="s">
         <v>214</v>
       </c>
-      <c r="J1" s="192" t="s">
+      <c r="J1" s="190" t="s">
         <v>215</v>
       </c>
-      <c r="K1" s="191" t="s">
+      <c r="K1" s="189" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="190" t="s">
+      <c r="L1" s="188" t="s">
         <v>177</v>
       </c>
-      <c r="M1" s="195" t="s">
+      <c r="M1" s="193" t="s">
         <v>178</v>
       </c>
-      <c r="N1" s="196" t="s">
+      <c r="N1" s="194" t="s">
         <v>179</v>
       </c>
-      <c r="O1" s="197" t="s">
+      <c r="O1" s="195" t="s">
         <v>216</v>
       </c>
-      <c r="P1" s="188" t="s">
+      <c r="P1" s="186" t="s">
         <v>217</v>
       </c>
-      <c r="Q1" s="198"/>
+      <c r="Q1" s="196"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="199"/>
-      <c r="B2" s="200"/>
-      <c r="C2" s="201"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="202"/>
-      <c r="I2" s="205"/>
-      <c r="J2" s="205"/>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205"/>
-      <c r="M2" s="207"/>
-      <c r="N2" s="207"/>
-      <c r="O2" s="206"/>
-      <c r="P2" s="205"/>
-      <c r="Q2" s="208"/>
+      <c r="A2" s="197"/>
+      <c r="B2" s="198"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="201"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="200"/>
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="203"/>
+      <c r="M2" s="205"/>
+      <c r="N2" s="205"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="206"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="209"/>
-      <c r="B3" s="210"/>
-      <c r="C3" s="211"/>
-      <c r="D3" s="202"/>
-      <c r="E3" s="202"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="202"/>
-      <c r="I3" s="213"/>
-      <c r="J3" s="213"/>
-      <c r="K3" s="213"/>
-      <c r="L3" s="206"/>
-      <c r="M3" s="213"/>
-      <c r="N3" s="214"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="214"/>
-      <c r="Q3" s="215"/>
+      <c r="A3" s="207"/>
+      <c r="B3" s="208"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="200"/>
+      <c r="E3" s="200"/>
+      <c r="F3" s="200"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="200"/>
+      <c r="I3" s="211"/>
+      <c r="J3" s="211"/>
+      <c r="K3" s="211"/>
+      <c r="L3" s="204"/>
+      <c r="M3" s="211"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="204"/>
+      <c r="P3" s="212"/>
+      <c r="Q3" s="213"/>
     </row>
     <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="199"/>
-      <c r="B4" s="210"/>
-      <c r="C4" s="211"/>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="212"/>
-      <c r="H4" s="202"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="206"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="214"/>
-      <c r="O4" s="206"/>
-      <c r="P4" s="214"/>
-      <c r="Q4" s="215"/>
+      <c r="A4" s="197"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="200"/>
+      <c r="E4" s="200"/>
+      <c r="F4" s="200"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="200"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="211"/>
+      <c r="K4" s="211"/>
+      <c r="L4" s="204"/>
+      <c r="M4" s="211"/>
+      <c r="N4" s="212"/>
+      <c r="O4" s="204"/>
+      <c r="P4" s="212"/>
+      <c r="Q4" s="213"/>
     </row>
     <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="216"/>
-      <c r="B5" s="217"/>
-      <c r="C5" s="218"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="212"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="213"/>
-      <c r="J5" s="213"/>
-      <c r="K5" s="213"/>
-      <c r="L5" s="206"/>
-      <c r="M5" s="213"/>
-      <c r="N5" s="214"/>
-      <c r="O5" s="206"/>
-      <c r="P5" s="214"/>
-      <c r="Q5" s="215"/>
+      <c r="A5" s="214"/>
+      <c r="B5" s="215"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="210"/>
+      <c r="H5" s="200"/>
+      <c r="I5" s="211"/>
+      <c r="J5" s="211"/>
+      <c r="K5" s="211"/>
+      <c r="L5" s="204"/>
+      <c r="M5" s="211"/>
+      <c r="N5" s="212"/>
+      <c r="O5" s="204"/>
+      <c r="P5" s="212"/>
+      <c r="Q5" s="213"/>
     </row>
     <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="209"/>
-      <c r="B6" s="203"/>
-      <c r="C6" s="219"/>
-      <c r="D6" s="202"/>
-      <c r="E6" s="202"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="212"/>
-      <c r="H6" s="202"/>
-      <c r="I6" s="213"/>
-      <c r="J6" s="213"/>
-      <c r="K6" s="213"/>
-      <c r="L6" s="206"/>
-      <c r="M6" s="220"/>
-      <c r="N6" s="221"/>
-      <c r="O6" s="206"/>
-      <c r="P6" s="221"/>
-      <c r="Q6" s="215"/>
+      <c r="A6" s="207"/>
+      <c r="B6" s="201"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="200"/>
+      <c r="E6" s="200"/>
+      <c r="F6" s="200"/>
+      <c r="G6" s="210"/>
+      <c r="H6" s="200"/>
+      <c r="I6" s="211"/>
+      <c r="J6" s="211"/>
+      <c r="K6" s="211"/>
+      <c r="L6" s="204"/>
+      <c r="M6" s="218"/>
+      <c r="N6" s="219"/>
+      <c r="O6" s="204"/>
+      <c r="P6" s="219"/>
+      <c r="Q6" s="213"/>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="211"/>
-      <c r="D7" s="202"/>
-      <c r="E7" s="202"/>
-      <c r="F7" s="202"/>
-      <c r="G7" s="212"/>
-      <c r="H7" s="202"/>
-      <c r="I7" s="221"/>
-      <c r="J7" s="220"/>
-      <c r="K7" s="220"/>
-      <c r="L7" s="206"/>
-      <c r="M7" s="220"/>
-      <c r="N7" s="221"/>
-      <c r="O7" s="206"/>
-      <c r="P7" s="221"/>
-      <c r="Q7" s="20"/>
+      <c r="A7" s="220"/>
+      <c r="B7" s="221"/>
+      <c r="C7" s="209"/>
+      <c r="D7" s="200"/>
+      <c r="E7" s="200"/>
+      <c r="F7" s="200"/>
+      <c r="G7" s="210"/>
+      <c r="H7" s="200"/>
+      <c r="I7" s="219"/>
+      <c r="J7" s="218"/>
+      <c r="K7" s="218"/>
+      <c r="L7" s="204"/>
+      <c r="M7" s="218"/>
+      <c r="N7" s="219"/>
+      <c r="O7" s="204"/>
+      <c r="P7" s="219"/>
+      <c r="Q7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="224"/>
-      <c r="B8" s="200"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="202"/>
-      <c r="E8" s="202"/>
-      <c r="F8" s="202"/>
-      <c r="G8" s="212"/>
-      <c r="H8" s="202"/>
-      <c r="I8" s="221"/>
-      <c r="J8" s="220"/>
-      <c r="K8" s="220"/>
-      <c r="L8" s="206"/>
-      <c r="M8" s="213"/>
-      <c r="N8" s="214"/>
-      <c r="O8" s="206"/>
-      <c r="P8" s="214"/>
-      <c r="Q8" s="20"/>
+      <c r="A8" s="222"/>
+      <c r="B8" s="198"/>
+      <c r="C8" s="209"/>
+      <c r="D8" s="200"/>
+      <c r="E8" s="200"/>
+      <c r="F8" s="200"/>
+      <c r="G8" s="210"/>
+      <c r="H8" s="200"/>
+      <c r="I8" s="219"/>
+      <c r="J8" s="218"/>
+      <c r="K8" s="218"/>
+      <c r="L8" s="204"/>
+      <c r="M8" s="211"/>
+      <c r="N8" s="212"/>
+      <c r="O8" s="204"/>
+      <c r="P8" s="212"/>
+      <c r="Q8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="225"/>
-      <c r="B9" s="226"/>
-      <c r="C9" s="211"/>
-      <c r="D9" s="202"/>
-      <c r="E9" s="202"/>
-      <c r="F9" s="202"/>
-      <c r="G9" s="212"/>
-      <c r="H9" s="202"/>
-      <c r="I9" s="221"/>
-      <c r="J9" s="220"/>
-      <c r="K9" s="220"/>
-      <c r="L9" s="206"/>
-      <c r="M9" s="220"/>
-      <c r="N9" s="221"/>
-      <c r="O9" s="206"/>
-      <c r="P9" s="227"/>
-      <c r="Q9" s="20"/>
+      <c r="A9" s="223"/>
+      <c r="B9" s="224"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="200"/>
+      <c r="E9" s="200"/>
+      <c r="F9" s="200"/>
+      <c r="G9" s="210"/>
+      <c r="H9" s="200"/>
+      <c r="I9" s="219"/>
+      <c r="J9" s="218"/>
+      <c r="K9" s="218"/>
+      <c r="L9" s="204"/>
+      <c r="M9" s="218"/>
+      <c r="N9" s="219"/>
+      <c r="O9" s="204"/>
+      <c r="P9" s="225"/>
+      <c r="Q9" s="19"/>
     </row>
     <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="225"/>
-      <c r="B10" s="228"/>
-      <c r="C10" s="211"/>
-      <c r="D10" s="202"/>
-      <c r="E10" s="202"/>
-      <c r="F10" s="202"/>
-      <c r="G10" s="212"/>
-      <c r="H10" s="202"/>
-      <c r="I10" s="221"/>
-      <c r="J10" s="220"/>
-      <c r="K10" s="220"/>
-      <c r="L10" s="206"/>
-      <c r="M10" s="220"/>
-      <c r="N10" s="221"/>
-      <c r="O10" s="206"/>
-      <c r="P10" s="227"/>
-      <c r="Q10" s="20"/>
+      <c r="A10" s="223"/>
+      <c r="B10" s="226"/>
+      <c r="C10" s="209"/>
+      <c r="D10" s="200"/>
+      <c r="E10" s="200"/>
+      <c r="F10" s="200"/>
+      <c r="G10" s="210"/>
+      <c r="H10" s="200"/>
+      <c r="I10" s="219"/>
+      <c r="J10" s="218"/>
+      <c r="K10" s="218"/>
+      <c r="L10" s="204"/>
+      <c r="M10" s="218"/>
+      <c r="N10" s="219"/>
+      <c r="O10" s="204"/>
+      <c r="P10" s="225"/>
+      <c r="Q10" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="225"/>
-      <c r="B11" s="229"/>
-      <c r="C11" s="211"/>
-      <c r="D11" s="202"/>
-      <c r="E11" s="202"/>
-      <c r="F11" s="202"/>
-      <c r="G11" s="212"/>
-      <c r="H11" s="202"/>
-      <c r="I11" s="221"/>
-      <c r="J11" s="220"/>
-      <c r="K11" s="220"/>
-      <c r="L11" s="206"/>
-      <c r="M11" s="220"/>
-      <c r="N11" s="221"/>
-      <c r="O11" s="206"/>
-      <c r="P11" s="227"/>
-      <c r="Q11" s="20"/>
+      <c r="A11" s="223"/>
+      <c r="B11" s="227"/>
+      <c r="C11" s="209"/>
+      <c r="D11" s="200"/>
+      <c r="E11" s="200"/>
+      <c r="F11" s="200"/>
+      <c r="G11" s="210"/>
+      <c r="H11" s="200"/>
+      <c r="I11" s="219"/>
+      <c r="J11" s="218"/>
+      <c r="K11" s="218"/>
+      <c r="L11" s="204"/>
+      <c r="M11" s="218"/>
+      <c r="N11" s="219"/>
+      <c r="O11" s="204"/>
+      <c r="P11" s="225"/>
+      <c r="Q11" s="19"/>
     </row>
     <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="225"/>
-      <c r="B12" s="226"/>
-      <c r="C12" s="211"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="202"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="202"/>
-      <c r="I12" s="221"/>
-      <c r="J12" s="220"/>
-      <c r="K12" s="220"/>
-      <c r="L12" s="206"/>
-      <c r="M12" s="220"/>
-      <c r="N12" s="221"/>
-      <c r="O12" s="206"/>
-      <c r="P12" s="227"/>
-      <c r="Q12" s="20"/>
+      <c r="A12" s="223"/>
+      <c r="B12" s="224"/>
+      <c r="C12" s="209"/>
+      <c r="D12" s="200"/>
+      <c r="E12" s="200"/>
+      <c r="F12" s="200"/>
+      <c r="G12" s="210"/>
+      <c r="H12" s="200"/>
+      <c r="I12" s="219"/>
+      <c r="J12" s="218"/>
+      <c r="K12" s="218"/>
+      <c r="L12" s="204"/>
+      <c r="M12" s="218"/>
+      <c r="N12" s="219"/>
+      <c r="O12" s="204"/>
+      <c r="P12" s="225"/>
+      <c r="Q12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="225"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="218"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="202"/>
-      <c r="F13" s="202"/>
-      <c r="G13" s="212"/>
-      <c r="H13" s="202"/>
-      <c r="I13" s="221"/>
-      <c r="J13" s="220"/>
-      <c r="K13" s="220"/>
-      <c r="L13" s="206"/>
-      <c r="M13" s="220"/>
-      <c r="N13" s="221"/>
-      <c r="O13" s="206"/>
-      <c r="P13" s="221"/>
-      <c r="Q13" s="20"/>
+      <c r="A13" s="223"/>
+      <c r="B13" s="198"/>
+      <c r="C13" s="216"/>
+      <c r="D13" s="200"/>
+      <c r="E13" s="200"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="210"/>
+      <c r="H13" s="200"/>
+      <c r="I13" s="219"/>
+      <c r="J13" s="218"/>
+      <c r="K13" s="218"/>
+      <c r="L13" s="204"/>
+      <c r="M13" s="218"/>
+      <c r="N13" s="219"/>
+      <c r="O13" s="204"/>
+      <c r="P13" s="219"/>
+      <c r="Q13" s="19"/>
     </row>
     <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="225"/>
-      <c r="B14" s="230"/>
-      <c r="C14" s="219"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="202"/>
-      <c r="G14" s="212"/>
-      <c r="H14" s="202"/>
-      <c r="I14" s="221"/>
-      <c r="J14" s="220"/>
-      <c r="K14" s="220"/>
-      <c r="L14" s="206"/>
-      <c r="M14" s="220"/>
-      <c r="N14" s="221"/>
-      <c r="O14" s="206"/>
-      <c r="P14" s="221"/>
-      <c r="Q14" s="20"/>
+      <c r="A14" s="223"/>
+      <c r="B14" s="228"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="200"/>
+      <c r="E14" s="200"/>
+      <c r="F14" s="200"/>
+      <c r="G14" s="210"/>
+      <c r="H14" s="200"/>
+      <c r="I14" s="219"/>
+      <c r="J14" s="218"/>
+      <c r="K14" s="218"/>
+      <c r="L14" s="204"/>
+      <c r="M14" s="218"/>
+      <c r="N14" s="219"/>
+      <c r="O14" s="204"/>
+      <c r="P14" s="219"/>
+      <c r="Q14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="225"/>
-      <c r="B15" s="217"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
-      <c r="F15" s="202"/>
-      <c r="G15" s="212"/>
-      <c r="H15" s="202"/>
-      <c r="I15" s="221"/>
-      <c r="J15" s="220"/>
-      <c r="K15" s="220"/>
-      <c r="L15" s="206"/>
-      <c r="M15" s="220"/>
-      <c r="N15" s="221"/>
-      <c r="O15" s="206"/>
-      <c r="P15" s="221"/>
-      <c r="Q15" s="20"/>
+      <c r="A15" s="223"/>
+      <c r="B15" s="215"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="200"/>
+      <c r="G15" s="210"/>
+      <c r="H15" s="200"/>
+      <c r="I15" s="219"/>
+      <c r="J15" s="218"/>
+      <c r="K15" s="218"/>
+      <c r="L15" s="204"/>
+      <c r="M15" s="218"/>
+      <c r="N15" s="219"/>
+      <c r="O15" s="204"/>
+      <c r="P15" s="219"/>
+      <c r="Q15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="225"/>
-      <c r="B16" s="223"/>
-      <c r="C16" s="218"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="202"/>
-      <c r="F16" s="202"/>
-      <c r="G16" s="212"/>
-      <c r="H16" s="202"/>
-      <c r="I16" s="221"/>
-      <c r="J16" s="220"/>
-      <c r="K16" s="220"/>
-      <c r="L16" s="206"/>
-      <c r="M16" s="220"/>
-      <c r="N16" s="221"/>
-      <c r="O16" s="206"/>
-      <c r="P16" s="221"/>
-      <c r="Q16" s="20"/>
+      <c r="A16" s="223"/>
+      <c r="B16" s="221"/>
+      <c r="C16" s="216"/>
+      <c r="D16" s="200"/>
+      <c r="E16" s="200"/>
+      <c r="F16" s="200"/>
+      <c r="G16" s="210"/>
+      <c r="H16" s="200"/>
+      <c r="I16" s="219"/>
+      <c r="J16" s="218"/>
+      <c r="K16" s="218"/>
+      <c r="L16" s="204"/>
+      <c r="M16" s="218"/>
+      <c r="N16" s="219"/>
+      <c r="O16" s="204"/>
+      <c r="P16" s="219"/>
+      <c r="Q16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="225"/>
-      <c r="B17" s="223"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="202"/>
-      <c r="F17" s="202"/>
-      <c r="G17" s="212"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="221"/>
-      <c r="J17" s="220"/>
-      <c r="K17" s="220"/>
-      <c r="L17" s="206"/>
-      <c r="M17" s="220"/>
-      <c r="N17" s="221"/>
-      <c r="O17" s="206"/>
-      <c r="P17" s="221"/>
-      <c r="Q17" s="20"/>
+      <c r="A17" s="223"/>
+      <c r="B17" s="221"/>
+      <c r="C17" s="199"/>
+      <c r="D17" s="200"/>
+      <c r="E17" s="200"/>
+      <c r="F17" s="200"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="200"/>
+      <c r="I17" s="219"/>
+      <c r="J17" s="218"/>
+      <c r="K17" s="218"/>
+      <c r="L17" s="204"/>
+      <c r="M17" s="218"/>
+      <c r="N17" s="219"/>
+      <c r="O17" s="204"/>
+      <c r="P17" s="219"/>
+      <c r="Q17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="225"/>
-      <c r="B18" s="200"/>
-      <c r="C18" s="218"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="202"/>
-      <c r="F18" s="202"/>
-      <c r="G18" s="212"/>
-      <c r="H18" s="202"/>
-      <c r="I18" s="221"/>
-      <c r="J18" s="220"/>
-      <c r="K18" s="220"/>
-      <c r="L18" s="206"/>
-      <c r="M18" s="220"/>
-      <c r="N18" s="221"/>
-      <c r="O18" s="206"/>
-      <c r="P18" s="221"/>
-      <c r="Q18" s="20"/>
+      <c r="A18" s="223"/>
+      <c r="B18" s="198"/>
+      <c r="C18" s="216"/>
+      <c r="D18" s="200"/>
+      <c r="E18" s="200"/>
+      <c r="F18" s="200"/>
+      <c r="G18" s="210"/>
+      <c r="H18" s="200"/>
+      <c r="I18" s="219"/>
+      <c r="J18" s="218"/>
+      <c r="K18" s="218"/>
+      <c r="L18" s="204"/>
+      <c r="M18" s="218"/>
+      <c r="N18" s="219"/>
+      <c r="O18" s="204"/>
+      <c r="P18" s="219"/>
+      <c r="Q18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="225"/>
-      <c r="B19" s="210"/>
-      <c r="C19" s="201"/>
-      <c r="D19" s="202"/>
-      <c r="E19" s="202"/>
-      <c r="F19" s="202"/>
-      <c r="G19" s="212"/>
-      <c r="H19" s="202"/>
-      <c r="I19" s="221"/>
-      <c r="J19" s="220"/>
-      <c r="K19" s="220"/>
-      <c r="L19" s="206"/>
-      <c r="M19" s="220"/>
-      <c r="N19" s="221"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="221"/>
-      <c r="Q19" s="20"/>
+      <c r="A19" s="223"/>
+      <c r="B19" s="208"/>
+      <c r="C19" s="199"/>
+      <c r="D19" s="200"/>
+      <c r="E19" s="200"/>
+      <c r="F19" s="200"/>
+      <c r="G19" s="210"/>
+      <c r="H19" s="200"/>
+      <c r="I19" s="219"/>
+      <c r="J19" s="218"/>
+      <c r="K19" s="218"/>
+      <c r="L19" s="204"/>
+      <c r="M19" s="218"/>
+      <c r="N19" s="219"/>
+      <c r="O19" s="204"/>
+      <c r="P19" s="219"/>
+      <c r="Q19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="225"/>
-      <c r="B20" s="217"/>
-      <c r="C20" s="211"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="202"/>
-      <c r="F20" s="202"/>
-      <c r="G20" s="202"/>
-      <c r="H20" s="202"/>
-      <c r="I20" s="221"/>
-      <c r="J20" s="220"/>
-      <c r="K20" s="220"/>
-      <c r="L20" s="206"/>
-      <c r="M20" s="220"/>
-      <c r="N20" s="221"/>
-      <c r="O20" s="206"/>
-      <c r="P20" s="221"/>
-      <c r="Q20" s="20"/>
+      <c r="A20" s="223"/>
+      <c r="B20" s="215"/>
+      <c r="C20" s="209"/>
+      <c r="D20" s="200"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="200"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="200"/>
+      <c r="I20" s="219"/>
+      <c r="J20" s="218"/>
+      <c r="K20" s="218"/>
+      <c r="L20" s="204"/>
+      <c r="M20" s="218"/>
+      <c r="N20" s="219"/>
+      <c r="O20" s="204"/>
+      <c r="P20" s="219"/>
+      <c r="Q20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="225"/>
-      <c r="B21" s="200"/>
-      <c r="C21" s="218"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="202"/>
-      <c r="F21" s="202"/>
-      <c r="G21" s="212"/>
-      <c r="H21" s="202"/>
-      <c r="I21" s="221"/>
-      <c r="J21" s="220"/>
-      <c r="K21" s="220"/>
-      <c r="L21" s="206"/>
-      <c r="M21" s="220"/>
-      <c r="N21" s="221"/>
-      <c r="O21" s="206"/>
-      <c r="P21" s="221"/>
-      <c r="Q21" s="20"/>
+      <c r="A21" s="223"/>
+      <c r="B21" s="198"/>
+      <c r="C21" s="216"/>
+      <c r="D21" s="200"/>
+      <c r="E21" s="200"/>
+      <c r="F21" s="200"/>
+      <c r="G21" s="210"/>
+      <c r="H21" s="200"/>
+      <c r="I21" s="219"/>
+      <c r="J21" s="218"/>
+      <c r="K21" s="218"/>
+      <c r="L21" s="204"/>
+      <c r="M21" s="218"/>
+      <c r="N21" s="219"/>
+      <c r="O21" s="204"/>
+      <c r="P21" s="219"/>
+      <c r="Q21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="225"/>
-      <c r="B22" s="210"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="202"/>
-      <c r="F22" s="202"/>
-      <c r="G22" s="212"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="221"/>
-      <c r="J22" s="220"/>
-      <c r="K22" s="220"/>
-      <c r="L22" s="206"/>
-      <c r="M22" s="220"/>
-      <c r="N22" s="221"/>
-      <c r="O22" s="206"/>
-      <c r="P22" s="221"/>
-      <c r="Q22" s="20"/>
+      <c r="A22" s="223"/>
+      <c r="B22" s="208"/>
+      <c r="C22" s="199"/>
+      <c r="D22" s="200"/>
+      <c r="E22" s="200"/>
+      <c r="F22" s="200"/>
+      <c r="G22" s="210"/>
+      <c r="H22" s="200"/>
+      <c r="I22" s="219"/>
+      <c r="J22" s="218"/>
+      <c r="K22" s="218"/>
+      <c r="L22" s="204"/>
+      <c r="M22" s="218"/>
+      <c r="N22" s="219"/>
+      <c r="O22" s="204"/>
+      <c r="P22" s="219"/>
+      <c r="Q22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="231"/>
-      <c r="B23" s="217"/>
-      <c r="C23" s="211"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="202"/>
-      <c r="F23" s="202"/>
-      <c r="G23" s="212"/>
-      <c r="H23" s="202"/>
-      <c r="I23" s="221"/>
-      <c r="J23" s="220"/>
-      <c r="K23" s="220"/>
-      <c r="L23" s="206"/>
-      <c r="M23" s="220"/>
-      <c r="N23" s="221"/>
-      <c r="O23" s="206"/>
-      <c r="P23" s="221"/>
-      <c r="Q23" s="20"/>
+      <c r="A23" s="229"/>
+      <c r="B23" s="215"/>
+      <c r="C23" s="209"/>
+      <c r="D23" s="200"/>
+      <c r="E23" s="200"/>
+      <c r="F23" s="200"/>
+      <c r="G23" s="210"/>
+      <c r="H23" s="200"/>
+      <c r="I23" s="219"/>
+      <c r="J23" s="218"/>
+      <c r="K23" s="218"/>
+      <c r="L23" s="204"/>
+      <c r="M23" s="218"/>
+      <c r="N23" s="219"/>
+      <c r="O23" s="204"/>
+      <c r="P23" s="219"/>
+      <c r="Q23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="232"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="211"/>
-      <c r="D24" s="202"/>
-      <c r="E24" s="202"/>
-      <c r="F24" s="202"/>
-      <c r="G24" s="212"/>
-      <c r="H24" s="202"/>
-      <c r="I24" s="221"/>
-      <c r="J24" s="220"/>
-      <c r="K24" s="202"/>
-      <c r="L24" s="206"/>
-      <c r="M24" s="220"/>
-      <c r="N24" s="221"/>
-      <c r="O24" s="206"/>
-      <c r="P24" s="221"/>
-      <c r="Q24" s="20"/>
+      <c r="A24" s="230"/>
+      <c r="B24" s="198"/>
+      <c r="C24" s="209"/>
+      <c r="D24" s="200"/>
+      <c r="E24" s="200"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="210"/>
+      <c r="H24" s="200"/>
+      <c r="I24" s="219"/>
+      <c r="J24" s="218"/>
+      <c r="K24" s="200"/>
+      <c r="L24" s="204"/>
+      <c r="M24" s="218"/>
+      <c r="N24" s="219"/>
+      <c r="O24" s="204"/>
+      <c r="P24" s="219"/>
+      <c r="Q24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="231"/>
-      <c r="B25" s="217"/>
-      <c r="C25" s="211"/>
-      <c r="D25" s="202"/>
-      <c r="E25" s="202"/>
-      <c r="F25" s="202"/>
-      <c r="G25" s="212"/>
-      <c r="H25" s="202"/>
-      <c r="I25" s="221"/>
-      <c r="J25" s="220"/>
-      <c r="K25" s="220"/>
-      <c r="L25" s="206"/>
-      <c r="M25" s="220"/>
-      <c r="N25" s="221"/>
-      <c r="O25" s="206"/>
-      <c r="P25" s="221"/>
-      <c r="Q25" s="20"/>
+      <c r="A25" s="229"/>
+      <c r="B25" s="215"/>
+      <c r="C25" s="209"/>
+      <c r="D25" s="200"/>
+      <c r="E25" s="200"/>
+      <c r="F25" s="200"/>
+      <c r="G25" s="210"/>
+      <c r="H25" s="200"/>
+      <c r="I25" s="219"/>
+      <c r="J25" s="218"/>
+      <c r="K25" s="218"/>
+      <c r="L25" s="204"/>
+      <c r="M25" s="218"/>
+      <c r="N25" s="219"/>
+      <c r="O25" s="204"/>
+      <c r="P25" s="219"/>
+      <c r="Q25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="222"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="211"/>
-      <c r="D26" s="202"/>
-      <c r="E26" s="202"/>
-      <c r="F26" s="202"/>
-      <c r="G26" s="212"/>
-      <c r="H26" s="202"/>
-      <c r="I26" s="221"/>
-      <c r="J26" s="220"/>
-      <c r="K26" s="202"/>
-      <c r="L26" s="206"/>
-      <c r="M26" s="220"/>
-      <c r="N26" s="221"/>
-      <c r="O26" s="206"/>
-      <c r="P26" s="221"/>
-      <c r="Q26" s="20"/>
+      <c r="A26" s="220"/>
+      <c r="B26" s="198"/>
+      <c r="C26" s="209"/>
+      <c r="D26" s="200"/>
+      <c r="E26" s="200"/>
+      <c r="F26" s="200"/>
+      <c r="G26" s="210"/>
+      <c r="H26" s="200"/>
+      <c r="I26" s="219"/>
+      <c r="J26" s="218"/>
+      <c r="K26" s="200"/>
+      <c r="L26" s="204"/>
+      <c r="M26" s="218"/>
+      <c r="N26" s="219"/>
+      <c r="O26" s="204"/>
+      <c r="P26" s="219"/>
+      <c r="Q26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="225"/>
-      <c r="B27" s="210"/>
-      <c r="C27" s="211"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="202"/>
-      <c r="F27" s="202"/>
-      <c r="G27" s="212"/>
-      <c r="H27" s="202"/>
-      <c r="I27" s="221"/>
-      <c r="J27" s="220"/>
-      <c r="K27" s="220"/>
-      <c r="L27" s="206"/>
-      <c r="M27" s="220"/>
-      <c r="N27" s="221"/>
-      <c r="O27" s="206"/>
-      <c r="P27" s="221"/>
-      <c r="Q27" s="20"/>
+      <c r="A27" s="223"/>
+      <c r="B27" s="208"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="200"/>
+      <c r="E27" s="200"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="210"/>
+      <c r="H27" s="200"/>
+      <c r="I27" s="219"/>
+      <c r="J27" s="218"/>
+      <c r="K27" s="218"/>
+      <c r="L27" s="204"/>
+      <c r="M27" s="218"/>
+      <c r="N27" s="219"/>
+      <c r="O27" s="204"/>
+      <c r="P27" s="219"/>
+      <c r="Q27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="231"/>
-      <c r="B28" s="233"/>
-      <c r="C28" s="211"/>
-      <c r="D28" s="202"/>
-      <c r="E28" s="202"/>
-      <c r="F28" s="202"/>
-      <c r="G28" s="212"/>
-      <c r="H28" s="202"/>
-      <c r="I28" s="221"/>
-      <c r="J28" s="220"/>
-      <c r="K28" s="220"/>
-      <c r="L28" s="206"/>
-      <c r="M28" s="220"/>
-      <c r="N28" s="221"/>
-      <c r="O28" s="206"/>
-      <c r="P28" s="227"/>
-      <c r="Q28" s="20"/>
+      <c r="A28" s="229"/>
+      <c r="B28" s="231"/>
+      <c r="C28" s="209"/>
+      <c r="D28" s="200"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="200"/>
+      <c r="I28" s="219"/>
+      <c r="J28" s="218"/>
+      <c r="K28" s="218"/>
+      <c r="L28" s="204"/>
+      <c r="M28" s="218"/>
+      <c r="N28" s="219"/>
+      <c r="O28" s="204"/>
+      <c r="P28" s="225"/>
+      <c r="Q28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="234"/>
-      <c r="B29" s="233"/>
-      <c r="C29" s="218"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="202"/>
-      <c r="F29" s="202"/>
-      <c r="G29" s="212"/>
-      <c r="H29" s="202"/>
-      <c r="I29" s="221"/>
-      <c r="J29" s="220"/>
-      <c r="K29" s="220"/>
-      <c r="L29" s="206"/>
-      <c r="M29" s="220"/>
-      <c r="N29" s="221"/>
-      <c r="O29" s="206"/>
-      <c r="P29" s="227"/>
-      <c r="Q29" s="20"/>
+      <c r="A29" s="232"/>
+      <c r="B29" s="231"/>
+      <c r="C29" s="216"/>
+      <c r="D29" s="200"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="210"/>
+      <c r="H29" s="200"/>
+      <c r="I29" s="219"/>
+      <c r="J29" s="218"/>
+      <c r="K29" s="218"/>
+      <c r="L29" s="204"/>
+      <c r="M29" s="218"/>
+      <c r="N29" s="219"/>
+      <c r="O29" s="204"/>
+      <c r="P29" s="225"/>
+      <c r="Q29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="234"/>
-      <c r="B30" s="210"/>
-      <c r="C30" s="201"/>
-      <c r="D30" s="202"/>
-      <c r="E30" s="202"/>
-      <c r="F30" s="202"/>
-      <c r="G30" s="212"/>
-      <c r="H30" s="202"/>
-      <c r="I30" s="221"/>
-      <c r="J30" s="220"/>
-      <c r="K30" s="220"/>
-      <c r="L30" s="206"/>
-      <c r="M30" s="220"/>
-      <c r="N30" s="221"/>
-      <c r="O30" s="206"/>
-      <c r="P30" s="221"/>
-      <c r="Q30" s="20"/>
+      <c r="A30" s="232"/>
+      <c r="B30" s="208"/>
+      <c r="C30" s="199"/>
+      <c r="D30" s="200"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="200"/>
+      <c r="G30" s="210"/>
+      <c r="H30" s="200"/>
+      <c r="I30" s="219"/>
+      <c r="J30" s="218"/>
+      <c r="K30" s="218"/>
+      <c r="L30" s="204"/>
+      <c r="M30" s="218"/>
+      <c r="N30" s="219"/>
+      <c r="O30" s="204"/>
+      <c r="P30" s="219"/>
+      <c r="Q30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="234"/>
-      <c r="B31" s="210"/>
-      <c r="C31" s="211"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="202"/>
-      <c r="F31" s="202"/>
-      <c r="G31" s="212"/>
-      <c r="H31" s="202"/>
-      <c r="I31" s="221"/>
-      <c r="J31" s="220"/>
-      <c r="K31" s="220"/>
-      <c r="L31" s="206"/>
-      <c r="M31" s="220"/>
-      <c r="N31" s="221"/>
-      <c r="O31" s="206"/>
-      <c r="P31" s="221"/>
-      <c r="Q31" s="20"/>
+      <c r="A31" s="232"/>
+      <c r="B31" s="208"/>
+      <c r="C31" s="209"/>
+      <c r="D31" s="200"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="200"/>
+      <c r="G31" s="210"/>
+      <c r="H31" s="200"/>
+      <c r="I31" s="219"/>
+      <c r="J31" s="218"/>
+      <c r="K31" s="218"/>
+      <c r="L31" s="204"/>
+      <c r="M31" s="218"/>
+      <c r="N31" s="219"/>
+      <c r="O31" s="204"/>
+      <c r="P31" s="219"/>
+      <c r="Q31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="234"/>
-      <c r="B32" s="217"/>
-      <c r="C32" s="218"/>
-      <c r="D32" s="202"/>
-      <c r="E32" s="202"/>
-      <c r="F32" s="202"/>
-      <c r="G32" s="212"/>
-      <c r="H32" s="202"/>
-      <c r="I32" s="221"/>
-      <c r="J32" s="220"/>
-      <c r="K32" s="220"/>
-      <c r="L32" s="206"/>
-      <c r="M32" s="220"/>
-      <c r="N32" s="221"/>
-      <c r="O32" s="206"/>
-      <c r="P32" s="221"/>
-      <c r="Q32" s="20"/>
+      <c r="A32" s="232"/>
+      <c r="B32" s="215"/>
+      <c r="C32" s="216"/>
+      <c r="D32" s="200"/>
+      <c r="E32" s="200"/>
+      <c r="F32" s="200"/>
+      <c r="G32" s="210"/>
+      <c r="H32" s="200"/>
+      <c r="I32" s="219"/>
+      <c r="J32" s="218"/>
+      <c r="K32" s="218"/>
+      <c r="L32" s="204"/>
+      <c r="M32" s="218"/>
+      <c r="N32" s="219"/>
+      <c r="O32" s="204"/>
+      <c r="P32" s="219"/>
+      <c r="Q32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="234"/>
-      <c r="B33" s="200"/>
-      <c r="C33" s="201"/>
-      <c r="D33" s="202"/>
-      <c r="E33" s="202"/>
-      <c r="F33" s="202"/>
-      <c r="G33" s="212"/>
-      <c r="H33" s="202"/>
-      <c r="I33" s="221"/>
-      <c r="J33" s="220"/>
-      <c r="K33" s="220"/>
-      <c r="L33" s="206"/>
-      <c r="M33" s="220"/>
-      <c r="N33" s="221"/>
-      <c r="O33" s="206"/>
-      <c r="P33" s="221"/>
-      <c r="Q33" s="20"/>
+      <c r="A33" s="232"/>
+      <c r="B33" s="198"/>
+      <c r="C33" s="199"/>
+      <c r="D33" s="200"/>
+      <c r="E33" s="200"/>
+      <c r="F33" s="200"/>
+      <c r="G33" s="210"/>
+      <c r="H33" s="200"/>
+      <c r="I33" s="219"/>
+      <c r="J33" s="218"/>
+      <c r="K33" s="218"/>
+      <c r="L33" s="204"/>
+      <c r="M33" s="218"/>
+      <c r="N33" s="219"/>
+      <c r="O33" s="204"/>
+      <c r="P33" s="219"/>
+      <c r="Q33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="234"/>
-      <c r="B34" s="210"/>
-      <c r="C34" s="211"/>
-      <c r="D34" s="202"/>
-      <c r="E34" s="202"/>
-      <c r="F34" s="202"/>
-      <c r="G34" s="212"/>
-      <c r="H34" s="202"/>
-      <c r="I34" s="221"/>
-      <c r="J34" s="220"/>
-      <c r="K34" s="220"/>
-      <c r="L34" s="206"/>
-      <c r="M34" s="220"/>
-      <c r="N34" s="221"/>
-      <c r="O34" s="206"/>
-      <c r="P34" s="221"/>
-      <c r="Q34" s="20"/>
+      <c r="A34" s="232"/>
+      <c r="B34" s="208"/>
+      <c r="C34" s="209"/>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="200"/>
+      <c r="G34" s="210"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="219"/>
+      <c r="J34" s="218"/>
+      <c r="K34" s="218"/>
+      <c r="L34" s="204"/>
+      <c r="M34" s="218"/>
+      <c r="N34" s="219"/>
+      <c r="O34" s="204"/>
+      <c r="P34" s="219"/>
+      <c r="Q34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="232"/>
-      <c r="B35" s="210"/>
-      <c r="C35" s="218"/>
-      <c r="D35" s="202"/>
-      <c r="E35" s="202"/>
-      <c r="F35" s="202"/>
-      <c r="G35" s="212"/>
-      <c r="H35" s="202"/>
-      <c r="I35" s="221"/>
-      <c r="J35" s="220"/>
-      <c r="K35" s="220"/>
-      <c r="L35" s="206"/>
-      <c r="M35" s="220"/>
-      <c r="N35" s="221"/>
-      <c r="O35" s="206"/>
-      <c r="P35" s="221"/>
-      <c r="Q35" s="20"/>
+      <c r="A35" s="230"/>
+      <c r="B35" s="208"/>
+      <c r="C35" s="216"/>
+      <c r="D35" s="200"/>
+      <c r="E35" s="200"/>
+      <c r="F35" s="200"/>
+      <c r="G35" s="210"/>
+      <c r="H35" s="200"/>
+      <c r="I35" s="219"/>
+      <c r="J35" s="218"/>
+      <c r="K35" s="218"/>
+      <c r="L35" s="204"/>
+      <c r="M35" s="218"/>
+      <c r="N35" s="219"/>
+      <c r="O35" s="204"/>
+      <c r="P35" s="219"/>
+      <c r="Q35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="231"/>
-      <c r="B36" s="210"/>
-      <c r="C36" s="201"/>
-      <c r="D36" s="202"/>
-      <c r="E36" s="202"/>
-      <c r="F36" s="220"/>
-      <c r="G36" s="212"/>
-      <c r="H36" s="202"/>
-      <c r="I36" s="221"/>
-      <c r="J36" s="220"/>
-      <c r="K36" s="220"/>
-      <c r="L36" s="206"/>
-      <c r="M36" s="220"/>
-      <c r="N36" s="221"/>
-      <c r="O36" s="206"/>
-      <c r="P36" s="221"/>
-      <c r="Q36" s="20"/>
+      <c r="A36" s="229"/>
+      <c r="B36" s="208"/>
+      <c r="C36" s="199"/>
+      <c r="D36" s="200"/>
+      <c r="E36" s="200"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="210"/>
+      <c r="H36" s="200"/>
+      <c r="I36" s="219"/>
+      <c r="J36" s="218"/>
+      <c r="K36" s="218"/>
+      <c r="L36" s="204"/>
+      <c r="M36" s="218"/>
+      <c r="N36" s="219"/>
+      <c r="O36" s="204"/>
+      <c r="P36" s="219"/>
+      <c r="Q36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="235"/>
-      <c r="B37" s="217"/>
-      <c r="C37" s="211"/>
-      <c r="D37" s="202"/>
-      <c r="E37" s="202"/>
-      <c r="F37" s="202"/>
-      <c r="G37" s="212"/>
-      <c r="H37" s="202"/>
-      <c r="I37" s="236"/>
-      <c r="J37" s="236"/>
-      <c r="K37" s="220"/>
-      <c r="L37" s="206"/>
-      <c r="M37" s="236"/>
-      <c r="N37" s="227"/>
-      <c r="O37" s="227"/>
-      <c r="P37" s="227"/>
-      <c r="Q37" s="237"/>
+      <c r="A37" s="233"/>
+      <c r="B37" s="215"/>
+      <c r="C37" s="209"/>
+      <c r="D37" s="200"/>
+      <c r="E37" s="200"/>
+      <c r="F37" s="200"/>
+      <c r="G37" s="210"/>
+      <c r="H37" s="200"/>
+      <c r="I37" s="234"/>
+      <c r="J37" s="234"/>
+      <c r="K37" s="218"/>
+      <c r="L37" s="204"/>
+      <c r="M37" s="234"/>
+      <c r="N37" s="225"/>
+      <c r="O37" s="225"/>
+      <c r="P37" s="225"/>
+      <c r="Q37" s="235"/>
     </row>
     <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="238"/>
-      <c r="B38" s="200"/>
-      <c r="C38" s="211"/>
-      <c r="D38" s="202"/>
-      <c r="E38" s="202"/>
-      <c r="F38" s="202"/>
-      <c r="G38" s="212"/>
-      <c r="H38" s="202"/>
-      <c r="I38" s="236"/>
-      <c r="J38" s="236"/>
-      <c r="K38" s="220"/>
-      <c r="L38" s="206"/>
-      <c r="M38" s="236"/>
-      <c r="N38" s="227"/>
-      <c r="O38" s="227"/>
-      <c r="P38" s="227"/>
-      <c r="Q38" s="237"/>
+      <c r="A38" s="236"/>
+      <c r="B38" s="198"/>
+      <c r="C38" s="209"/>
+      <c r="D38" s="200"/>
+      <c r="E38" s="200"/>
+      <c r="F38" s="200"/>
+      <c r="G38" s="210"/>
+      <c r="H38" s="200"/>
+      <c r="I38" s="234"/>
+      <c r="J38" s="234"/>
+      <c r="K38" s="218"/>
+      <c r="L38" s="204"/>
+      <c r="M38" s="234"/>
+      <c r="N38" s="225"/>
+      <c r="O38" s="225"/>
+      <c r="P38" s="225"/>
+      <c r="Q38" s="235"/>
     </row>
     <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="239"/>
-      <c r="B39" s="217"/>
-      <c r="C39" s="218"/>
-      <c r="D39" s="202"/>
-      <c r="E39" s="202"/>
-      <c r="F39" s="202"/>
-      <c r="G39" s="212"/>
-      <c r="H39" s="202"/>
-      <c r="I39" s="236"/>
-      <c r="J39" s="236"/>
-      <c r="K39" s="220"/>
-      <c r="L39" s="206"/>
-      <c r="M39" s="236"/>
-      <c r="N39" s="227"/>
-      <c r="O39" s="227"/>
-      <c r="P39" s="227"/>
-      <c r="Q39" s="237"/>
+      <c r="A39" s="237"/>
+      <c r="B39" s="215"/>
+      <c r="C39" s="216"/>
+      <c r="D39" s="200"/>
+      <c r="E39" s="200"/>
+      <c r="F39" s="200"/>
+      <c r="G39" s="210"/>
+      <c r="H39" s="200"/>
+      <c r="I39" s="234"/>
+      <c r="J39" s="234"/>
+      <c r="K39" s="218"/>
+      <c r="L39" s="204"/>
+      <c r="M39" s="234"/>
+      <c r="N39" s="225"/>
+      <c r="O39" s="225"/>
+      <c r="P39" s="225"/>
+      <c r="Q39" s="235"/>
     </row>
     <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="235"/>
-      <c r="B40" s="200"/>
-      <c r="C40" s="240"/>
-      <c r="D40" s="202"/>
-      <c r="E40" s="202"/>
-      <c r="F40" s="202"/>
-      <c r="G40" s="212"/>
-      <c r="H40" s="202"/>
-      <c r="I40" s="236"/>
-      <c r="J40" s="236"/>
-      <c r="K40" s="220"/>
-      <c r="L40" s="206"/>
-      <c r="M40" s="236"/>
-      <c r="N40" s="227"/>
-      <c r="O40" s="227"/>
-      <c r="P40" s="227"/>
-      <c r="Q40" s="237"/>
+      <c r="A40" s="233"/>
+      <c r="B40" s="198"/>
+      <c r="C40" s="238"/>
+      <c r="D40" s="200"/>
+      <c r="E40" s="200"/>
+      <c r="F40" s="200"/>
+      <c r="G40" s="210"/>
+      <c r="H40" s="200"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="218"/>
+      <c r="L40" s="204"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="225"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="235"/>
     </row>
     <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="235"/>
-      <c r="B41" s="217"/>
-      <c r="C41" s="201"/>
-      <c r="D41" s="202"/>
-      <c r="E41" s="202"/>
-      <c r="F41" s="202"/>
-      <c r="G41" s="212"/>
-      <c r="H41" s="202"/>
-      <c r="I41" s="236"/>
-      <c r="J41" s="236"/>
-      <c r="K41" s="220"/>
-      <c r="L41" s="206"/>
-      <c r="M41" s="236"/>
-      <c r="N41" s="227"/>
-      <c r="O41" s="227"/>
-      <c r="P41" s="227"/>
-      <c r="Q41" s="237"/>
+      <c r="A41" s="233"/>
+      <c r="B41" s="215"/>
+      <c r="C41" s="199"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="200"/>
+      <c r="F41" s="200"/>
+      <c r="G41" s="210"/>
+      <c r="H41" s="200"/>
+      <c r="I41" s="234"/>
+      <c r="J41" s="234"/>
+      <c r="K41" s="218"/>
+      <c r="L41" s="204"/>
+      <c r="M41" s="234"/>
+      <c r="N41" s="225"/>
+      <c r="O41" s="225"/>
+      <c r="P41" s="225"/>
+      <c r="Q41" s="235"/>
     </row>
     <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="235"/>
-      <c r="B42" s="200"/>
-      <c r="C42" s="241"/>
-      <c r="D42" s="242"/>
-      <c r="E42" s="202"/>
-      <c r="F42" s="202"/>
-      <c r="G42" s="236"/>
-      <c r="H42" s="202"/>
-      <c r="I42" s="202"/>
-      <c r="J42" s="202"/>
-      <c r="K42" s="220"/>
-      <c r="L42" s="206"/>
-      <c r="M42" s="227"/>
-      <c r="N42" s="227"/>
-      <c r="O42" s="227"/>
-      <c r="P42" s="227"/>
-      <c r="Q42" s="237"/>
+      <c r="A42" s="233"/>
+      <c r="B42" s="198"/>
+      <c r="C42" s="239"/>
+      <c r="D42" s="240"/>
+      <c r="E42" s="200"/>
+      <c r="F42" s="200"/>
+      <c r="G42" s="234"/>
+      <c r="H42" s="200"/>
+      <c r="I42" s="200"/>
+      <c r="J42" s="200"/>
+      <c r="K42" s="218"/>
+      <c r="L42" s="204"/>
+      <c r="M42" s="225"/>
+      <c r="N42" s="225"/>
+      <c r="O42" s="225"/>
+      <c r="P42" s="225"/>
+      <c r="Q42" s="235"/>
     </row>
     <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="235"/>
-      <c r="B43" s="217"/>
-      <c r="C43" s="243"/>
-      <c r="D43" s="236"/>
-      <c r="E43" s="202"/>
-      <c r="F43" s="202"/>
-      <c r="G43" s="236"/>
-      <c r="H43" s="202"/>
-      <c r="I43" s="202"/>
-      <c r="J43" s="202"/>
-      <c r="K43" s="220"/>
-      <c r="L43" s="206"/>
-      <c r="M43" s="227"/>
-      <c r="N43" s="227"/>
-      <c r="O43" s="227"/>
-      <c r="P43" s="227"/>
-      <c r="Q43" s="237"/>
+      <c r="A43" s="233"/>
+      <c r="B43" s="215"/>
+      <c r="C43" s="241"/>
+      <c r="D43" s="234"/>
+      <c r="E43" s="200"/>
+      <c r="F43" s="200"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="200"/>
+      <c r="I43" s="200"/>
+      <c r="J43" s="200"/>
+      <c r="K43" s="218"/>
+      <c r="L43" s="204"/>
+      <c r="M43" s="225"/>
+      <c r="N43" s="225"/>
+      <c r="O43" s="225"/>
+      <c r="P43" s="225"/>
+      <c r="Q43" s="235"/>
     </row>
     <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="238"/>
-      <c r="B44" s="223"/>
-      <c r="C44" s="244"/>
-      <c r="D44" s="236"/>
-      <c r="E44" s="202"/>
-      <c r="F44" s="202"/>
-      <c r="G44" s="236"/>
-      <c r="H44" s="202"/>
-      <c r="I44" s="202"/>
-      <c r="J44" s="202"/>
-      <c r="K44" s="220"/>
-      <c r="L44" s="206"/>
-      <c r="M44" s="227"/>
-      <c r="N44" s="227"/>
-      <c r="O44" s="227"/>
-      <c r="P44" s="227"/>
-      <c r="Q44" s="237"/>
+      <c r="A44" s="236"/>
+      <c r="B44" s="221"/>
+      <c r="C44" s="242"/>
+      <c r="D44" s="234"/>
+      <c r="E44" s="200"/>
+      <c r="F44" s="200"/>
+      <c r="G44" s="234"/>
+      <c r="H44" s="200"/>
+      <c r="I44" s="200"/>
+      <c r="J44" s="200"/>
+      <c r="K44" s="218"/>
+      <c r="L44" s="204"/>
+      <c r="M44" s="225"/>
+      <c r="N44" s="225"/>
+      <c r="O44" s="225"/>
+      <c r="P44" s="225"/>
+      <c r="Q44" s="235"/>
     </row>
     <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="245"/>
-      <c r="B45" s="223"/>
-      <c r="C45" s="244"/>
-      <c r="D45" s="236"/>
-      <c r="E45" s="202"/>
-      <c r="F45" s="202"/>
-      <c r="G45" s="236"/>
-      <c r="H45" s="202"/>
-      <c r="I45" s="202"/>
-      <c r="J45" s="202"/>
-      <c r="K45" s="220"/>
-      <c r="L45" s="206"/>
-      <c r="M45" s="227"/>
-      <c r="N45" s="227"/>
-      <c r="O45" s="227"/>
-      <c r="P45" s="227"/>
-      <c r="Q45" s="237"/>
+      <c r="A45" s="243"/>
+      <c r="B45" s="221"/>
+      <c r="C45" s="242"/>
+      <c r="D45" s="234"/>
+      <c r="E45" s="200"/>
+      <c r="F45" s="200"/>
+      <c r="G45" s="234"/>
+      <c r="H45" s="200"/>
+      <c r="I45" s="200"/>
+      <c r="J45" s="200"/>
+      <c r="K45" s="218"/>
+      <c r="L45" s="204"/>
+      <c r="M45" s="225"/>
+      <c r="N45" s="225"/>
+      <c r="O45" s="225"/>
+      <c r="P45" s="225"/>
+      <c r="Q45" s="235"/>
     </row>
     <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="227"/>
-      <c r="B46" s="246"/>
-      <c r="C46" s="241"/>
-      <c r="D46" s="236"/>
-      <c r="E46" s="202"/>
-      <c r="F46" s="202"/>
-      <c r="G46" s="236"/>
-      <c r="H46" s="202"/>
-      <c r="I46" s="202"/>
-      <c r="J46" s="202"/>
-      <c r="K46" s="220"/>
-      <c r="L46" s="206"/>
-      <c r="M46" s="227"/>
-      <c r="N46" s="227"/>
-      <c r="O46" s="227"/>
-      <c r="P46" s="227"/>
-      <c r="Q46" s="237"/>
+      <c r="A46" s="225"/>
+      <c r="B46" s="244"/>
+      <c r="C46" s="239"/>
+      <c r="D46" s="234"/>
+      <c r="E46" s="200"/>
+      <c r="F46" s="200"/>
+      <c r="G46" s="234"/>
+      <c r="H46" s="200"/>
+      <c r="I46" s="200"/>
+      <c r="J46" s="200"/>
+      <c r="K46" s="218"/>
+      <c r="L46" s="204"/>
+      <c r="M46" s="225"/>
+      <c r="N46" s="225"/>
+      <c r="O46" s="225"/>
+      <c r="P46" s="225"/>
+      <c r="Q46" s="235"/>
     </row>
     <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="238"/>
-      <c r="B47" s="217"/>
-      <c r="C47" s="243"/>
-      <c r="D47" s="236"/>
-      <c r="E47" s="202"/>
-      <c r="F47" s="202"/>
-      <c r="G47" s="236"/>
-      <c r="H47" s="202"/>
-      <c r="I47" s="202"/>
-      <c r="J47" s="202"/>
-      <c r="K47" s="220"/>
-      <c r="L47" s="206"/>
-      <c r="M47" s="227"/>
-      <c r="N47" s="227"/>
-      <c r="O47" s="227"/>
-      <c r="P47" s="227"/>
-      <c r="Q47" s="237"/>
+      <c r="A47" s="236"/>
+      <c r="B47" s="215"/>
+      <c r="C47" s="241"/>
+      <c r="D47" s="234"/>
+      <c r="E47" s="200"/>
+      <c r="F47" s="200"/>
+      <c r="G47" s="234"/>
+      <c r="H47" s="200"/>
+      <c r="I47" s="200"/>
+      <c r="J47" s="200"/>
+      <c r="K47" s="218"/>
+      <c r="L47" s="204"/>
+      <c r="M47" s="225"/>
+      <c r="N47" s="225"/>
+      <c r="O47" s="225"/>
+      <c r="P47" s="225"/>
+      <c r="Q47" s="235"/>
     </row>
     <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="227"/>
-      <c r="B48" s="246"/>
-      <c r="C48" s="244"/>
-      <c r="D48" s="236"/>
-      <c r="E48" s="202"/>
-      <c r="F48" s="202"/>
-      <c r="G48" s="236"/>
-      <c r="H48" s="202"/>
-      <c r="I48" s="202"/>
-      <c r="J48" s="202"/>
-      <c r="K48" s="220"/>
-      <c r="L48" s="206"/>
-      <c r="M48" s="227"/>
-      <c r="N48" s="227"/>
-      <c r="O48" s="227"/>
-      <c r="P48" s="227"/>
-      <c r="Q48" s="237"/>
+      <c r="A48" s="225"/>
+      <c r="B48" s="244"/>
+      <c r="C48" s="242"/>
+      <c r="D48" s="234"/>
+      <c r="E48" s="200"/>
+      <c r="F48" s="200"/>
+      <c r="G48" s="234"/>
+      <c r="H48" s="200"/>
+      <c r="I48" s="200"/>
+      <c r="J48" s="200"/>
+      <c r="K48" s="218"/>
+      <c r="L48" s="204"/>
+      <c r="M48" s="225"/>
+      <c r="N48" s="225"/>
+      <c r="O48" s="225"/>
+      <c r="P48" s="225"/>
+      <c r="Q48" s="235"/>
     </row>
     <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="238"/>
-      <c r="B49" s="217"/>
-      <c r="C49" s="239"/>
-      <c r="D49" s="236"/>
-      <c r="E49" s="202"/>
-      <c r="F49" s="202"/>
-      <c r="G49" s="236"/>
-      <c r="H49" s="202"/>
-      <c r="I49" s="202"/>
-      <c r="J49" s="202"/>
-      <c r="K49" s="220"/>
-      <c r="L49" s="206"/>
-      <c r="M49" s="227"/>
-      <c r="N49" s="227"/>
-      <c r="O49" s="227"/>
-      <c r="P49" s="227"/>
-      <c r="Q49" s="237"/>
+      <c r="A49" s="236"/>
+      <c r="B49" s="215"/>
+      <c r="C49" s="237"/>
+      <c r="D49" s="234"/>
+      <c r="E49" s="200"/>
+      <c r="F49" s="200"/>
+      <c r="G49" s="234"/>
+      <c r="H49" s="200"/>
+      <c r="I49" s="200"/>
+      <c r="J49" s="200"/>
+      <c r="K49" s="218"/>
+      <c r="L49" s="204"/>
+      <c r="M49" s="225"/>
+      <c r="N49" s="225"/>
+      <c r="O49" s="225"/>
+      <c r="P49" s="225"/>
+      <c r="Q49" s="235"/>
     </row>
     <row r="50" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="247"/>
-      <c r="B50" s="248"/>
-      <c r="C50" s="238"/>
-      <c r="D50" s="236"/>
-      <c r="E50" s="202"/>
-      <c r="F50" s="202"/>
-      <c r="G50" s="236"/>
-      <c r="H50" s="202"/>
-      <c r="I50" s="202"/>
-      <c r="J50" s="202"/>
-      <c r="K50" s="220"/>
-      <c r="L50" s="206"/>
-      <c r="M50" s="227"/>
-      <c r="N50" s="227"/>
-      <c r="O50" s="227"/>
-      <c r="P50" s="227"/>
-      <c r="Q50" s="237"/>
+      <c r="A50" s="245"/>
+      <c r="B50" s="246"/>
+      <c r="C50" s="236"/>
+      <c r="D50" s="234"/>
+      <c r="E50" s="200"/>
+      <c r="F50" s="200"/>
+      <c r="G50" s="234"/>
+      <c r="H50" s="200"/>
+      <c r="I50" s="200"/>
+      <c r="J50" s="200"/>
+      <c r="K50" s="218"/>
+      <c r="L50" s="204"/>
+      <c r="M50" s="225"/>
+      <c r="N50" s="225"/>
+      <c r="O50" s="225"/>
+      <c r="P50" s="225"/>
+      <c r="Q50" s="235"/>
     </row>
     <row r="51" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="227"/>
-      <c r="B51" s="246"/>
-      <c r="C51" s="239"/>
-      <c r="D51" s="236"/>
-      <c r="E51" s="202"/>
-      <c r="F51" s="202"/>
-      <c r="G51" s="236"/>
-      <c r="H51" s="202"/>
-      <c r="I51" s="202"/>
-      <c r="J51" s="202"/>
-      <c r="K51" s="220"/>
-      <c r="L51" s="206"/>
-      <c r="M51" s="227"/>
-      <c r="N51" s="227"/>
-      <c r="O51" s="227"/>
-      <c r="P51" s="227"/>
-      <c r="Q51" s="237"/>
+      <c r="A51" s="225"/>
+      <c r="B51" s="244"/>
+      <c r="C51" s="237"/>
+      <c r="D51" s="234"/>
+      <c r="E51" s="200"/>
+      <c r="F51" s="200"/>
+      <c r="G51" s="234"/>
+      <c r="H51" s="200"/>
+      <c r="I51" s="200"/>
+      <c r="J51" s="200"/>
+      <c r="K51" s="218"/>
+      <c r="L51" s="204"/>
+      <c r="M51" s="225"/>
+      <c r="N51" s="225"/>
+      <c r="O51" s="225"/>
+      <c r="P51" s="225"/>
+      <c r="Q51" s="235"/>
     </row>
     <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="238"/>
-      <c r="B52" s="210"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="236"/>
-      <c r="E52" s="202"/>
-      <c r="F52" s="202"/>
-      <c r="G52" s="236"/>
-      <c r="H52" s="202"/>
-      <c r="I52" s="202"/>
-      <c r="J52" s="202"/>
-      <c r="K52" s="220"/>
-      <c r="L52" s="206"/>
-      <c r="M52" s="227"/>
-      <c r="N52" s="227"/>
-      <c r="O52" s="227"/>
-      <c r="P52" s="227"/>
-      <c r="Q52" s="237"/>
+      <c r="A52" s="236"/>
+      <c r="B52" s="208"/>
+      <c r="C52" s="236"/>
+      <c r="D52" s="234"/>
+      <c r="E52" s="200"/>
+      <c r="F52" s="200"/>
+      <c r="G52" s="234"/>
+      <c r="H52" s="200"/>
+      <c r="I52" s="200"/>
+      <c r="J52" s="200"/>
+      <c r="K52" s="218"/>
+      <c r="L52" s="204"/>
+      <c r="M52" s="225"/>
+      <c r="N52" s="225"/>
+      <c r="O52" s="225"/>
+      <c r="P52" s="225"/>
+      <c r="Q52" s="235"/>
     </row>
     <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="245"/>
-      <c r="B53" s="217"/>
-      <c r="C53" s="245"/>
-      <c r="D53" s="236"/>
-      <c r="E53" s="202"/>
-      <c r="F53" s="202"/>
-      <c r="G53" s="236"/>
-      <c r="H53" s="202"/>
-      <c r="I53" s="202"/>
-      <c r="J53" s="202"/>
-      <c r="K53" s="220"/>
-      <c r="L53" s="206"/>
-      <c r="M53" s="227"/>
-      <c r="N53" s="227"/>
-      <c r="O53" s="227"/>
-      <c r="P53" s="227"/>
-      <c r="Q53" s="237"/>
+      <c r="A53" s="243"/>
+      <c r="B53" s="215"/>
+      <c r="C53" s="243"/>
+      <c r="D53" s="234"/>
+      <c r="E53" s="200"/>
+      <c r="F53" s="200"/>
+      <c r="G53" s="234"/>
+      <c r="H53" s="200"/>
+      <c r="I53" s="200"/>
+      <c r="J53" s="200"/>
+      <c r="K53" s="218"/>
+      <c r="L53" s="204"/>
+      <c r="M53" s="225"/>
+      <c r="N53" s="225"/>
+      <c r="O53" s="225"/>
+      <c r="P53" s="225"/>
+      <c r="Q53" s="235"/>
     </row>
     <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="245"/>
-      <c r="B54" s="223"/>
-      <c r="C54" s="239"/>
-      <c r="D54" s="236"/>
-      <c r="E54" s="202"/>
-      <c r="F54" s="202"/>
-      <c r="G54" s="236"/>
-      <c r="H54" s="202"/>
-      <c r="I54" s="202"/>
-      <c r="J54" s="202"/>
-      <c r="K54" s="220"/>
-      <c r="L54" s="206"/>
-      <c r="M54" s="227"/>
-      <c r="N54" s="227"/>
-      <c r="O54" s="227"/>
-      <c r="P54" s="227"/>
-      <c r="Q54" s="237"/>
+      <c r="A54" s="243"/>
+      <c r="B54" s="221"/>
+      <c r="C54" s="237"/>
+      <c r="D54" s="234"/>
+      <c r="E54" s="200"/>
+      <c r="F54" s="200"/>
+      <c r="G54" s="234"/>
+      <c r="H54" s="200"/>
+      <c r="I54" s="200"/>
+      <c r="J54" s="200"/>
+      <c r="K54" s="218"/>
+      <c r="L54" s="204"/>
+      <c r="M54" s="225"/>
+      <c r="N54" s="225"/>
+      <c r="O54" s="225"/>
+      <c r="P54" s="225"/>
+      <c r="Q54" s="235"/>
     </row>
     <row r="55" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="245"/>
-      <c r="B55" s="223"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="236"/>
-      <c r="E55" s="202"/>
-      <c r="F55" s="202"/>
-      <c r="G55" s="236"/>
-      <c r="H55" s="202"/>
-      <c r="I55" s="202"/>
-      <c r="J55" s="202"/>
-      <c r="K55" s="220"/>
-      <c r="L55" s="206"/>
-      <c r="M55" s="227"/>
-      <c r="N55" s="227"/>
-      <c r="O55" s="227"/>
-      <c r="P55" s="227"/>
-      <c r="Q55" s="237"/>
+      <c r="A55" s="243"/>
+      <c r="B55" s="221"/>
+      <c r="C55" s="236"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="200"/>
+      <c r="F55" s="200"/>
+      <c r="G55" s="234"/>
+      <c r="H55" s="200"/>
+      <c r="I55" s="200"/>
+      <c r="J55" s="200"/>
+      <c r="K55" s="218"/>
+      <c r="L55" s="204"/>
+      <c r="M55" s="225"/>
+      <c r="N55" s="225"/>
+      <c r="O55" s="225"/>
+      <c r="P55" s="225"/>
+      <c r="Q55" s="235"/>
     </row>
     <row r="56" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="247"/>
-      <c r="B56" s="246"/>
-      <c r="C56" s="245"/>
-      <c r="D56" s="236"/>
-      <c r="E56" s="202"/>
-      <c r="F56" s="202"/>
-      <c r="G56" s="236"/>
-      <c r="H56" s="202"/>
-      <c r="I56" s="202"/>
-      <c r="J56" s="202"/>
-      <c r="K56" s="220"/>
-      <c r="L56" s="206"/>
-      <c r="M56" s="227"/>
-      <c r="N56" s="227"/>
-      <c r="O56" s="227"/>
-      <c r="P56" s="227"/>
-      <c r="Q56" s="237"/>
+      <c r="A56" s="245"/>
+      <c r="B56" s="244"/>
+      <c r="C56" s="243"/>
+      <c r="D56" s="234"/>
+      <c r="E56" s="200"/>
+      <c r="F56" s="200"/>
+      <c r="G56" s="234"/>
+      <c r="H56" s="200"/>
+      <c r="I56" s="200"/>
+      <c r="J56" s="200"/>
+      <c r="K56" s="218"/>
+      <c r="L56" s="204"/>
+      <c r="M56" s="225"/>
+      <c r="N56" s="225"/>
+      <c r="O56" s="225"/>
+      <c r="P56" s="225"/>
+      <c r="Q56" s="235"/>
     </row>
     <row r="57" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="245"/>
-      <c r="B57" s="217"/>
-      <c r="C57" s="245"/>
-      <c r="D57" s="236"/>
-      <c r="E57" s="202"/>
-      <c r="F57" s="202"/>
-      <c r="G57" s="202"/>
-      <c r="H57" s="202"/>
-      <c r="I57" s="202"/>
-      <c r="J57" s="202"/>
-      <c r="K57" s="236"/>
-      <c r="L57" s="206"/>
-      <c r="M57" s="227"/>
-      <c r="N57" s="227"/>
-      <c r="O57" s="227"/>
-      <c r="P57" s="227"/>
-      <c r="Q57" s="237"/>
+      <c r="A57" s="243"/>
+      <c r="B57" s="215"/>
+      <c r="C57" s="243"/>
+      <c r="D57" s="234"/>
+      <c r="E57" s="200"/>
+      <c r="F57" s="200"/>
+      <c r="G57" s="200"/>
+      <c r="H57" s="200"/>
+      <c r="I57" s="200"/>
+      <c r="J57" s="200"/>
+      <c r="K57" s="234"/>
+      <c r="L57" s="204"/>
+      <c r="M57" s="225"/>
+      <c r="N57" s="225"/>
+      <c r="O57" s="225"/>
+      <c r="P57" s="225"/>
+      <c r="Q57" s="235"/>
     </row>
     <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="239"/>
-      <c r="B58" s="223"/>
-      <c r="C58" s="241"/>
-      <c r="D58" s="236"/>
-      <c r="E58" s="202"/>
-      <c r="F58" s="202"/>
-      <c r="G58" s="202"/>
-      <c r="H58" s="202"/>
-      <c r="I58" s="202"/>
-      <c r="J58" s="202"/>
-      <c r="K58" s="236"/>
-      <c r="L58" s="206"/>
-      <c r="M58" s="227"/>
-      <c r="N58" s="227"/>
-      <c r="O58" s="227"/>
-      <c r="P58" s="227"/>
-      <c r="Q58" s="237"/>
+      <c r="A58" s="237"/>
+      <c r="B58" s="221"/>
+      <c r="C58" s="239"/>
+      <c r="D58" s="234"/>
+      <c r="E58" s="200"/>
+      <c r="F58" s="200"/>
+      <c r="G58" s="200"/>
+      <c r="H58" s="200"/>
+      <c r="I58" s="200"/>
+      <c r="J58" s="200"/>
+      <c r="K58" s="234"/>
+      <c r="L58" s="204"/>
+      <c r="M58" s="225"/>
+      <c r="N58" s="225"/>
+      <c r="O58" s="225"/>
+      <c r="P58" s="225"/>
+      <c r="Q58" s="235"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="246"/>
-      <c r="B59" s="246"/>
-      <c r="C59" s="246"/>
-      <c r="D59" s="202"/>
-      <c r="E59" s="202"/>
-      <c r="F59" s="202"/>
-      <c r="G59" s="202"/>
-      <c r="H59" s="202"/>
-      <c r="I59" s="202"/>
-      <c r="J59" s="202"/>
-      <c r="K59" s="202"/>
-      <c r="L59" s="202"/>
-      <c r="M59" s="202"/>
-      <c r="N59" s="202"/>
-      <c r="O59" s="202"/>
-      <c r="P59" s="202"/>
+      <c r="A59" s="244"/>
+      <c r="B59" s="244"/>
+      <c r="C59" s="244"/>
+      <c r="D59" s="200"/>
+      <c r="E59" s="200"/>
+      <c r="F59" s="200"/>
+      <c r="G59" s="200"/>
+      <c r="H59" s="200"/>
+      <c r="I59" s="200"/>
+      <c r="J59" s="200"/>
+      <c r="K59" s="200"/>
+      <c r="L59" s="200"/>
+      <c r="M59" s="200"/>
+      <c r="N59" s="200"/>
+      <c r="O59" s="200"/>
+      <c r="P59" s="200"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="246"/>
-      <c r="B60" s="246"/>
-      <c r="C60" s="246"/>
-      <c r="D60" s="202"/>
-      <c r="E60" s="202"/>
-      <c r="F60" s="202"/>
-      <c r="G60" s="202"/>
-      <c r="H60" s="202"/>
-      <c r="I60" s="202"/>
-      <c r="J60" s="202"/>
-      <c r="K60" s="202"/>
-      <c r="L60" s="202"/>
-      <c r="M60" s="202"/>
-      <c r="N60" s="202"/>
-      <c r="O60" s="202"/>
-      <c r="P60" s="202"/>
+      <c r="A60" s="244"/>
+      <c r="B60" s="244"/>
+      <c r="C60" s="244"/>
+      <c r="D60" s="200"/>
+      <c r="E60" s="200"/>
+      <c r="F60" s="200"/>
+      <c r="G60" s="200"/>
+      <c r="H60" s="200"/>
+      <c r="I60" s="200"/>
+      <c r="J60" s="200"/>
+      <c r="K60" s="200"/>
+      <c r="L60" s="200"/>
+      <c r="M60" s="200"/>
+      <c r="N60" s="200"/>
+      <c r="O60" s="200"/>
+      <c r="P60" s="200"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="246"/>
-      <c r="B61" s="246"/>
-      <c r="C61" s="246"/>
-      <c r="D61" s="202"/>
-      <c r="E61" s="202"/>
-      <c r="F61" s="202"/>
-      <c r="G61" s="202"/>
-      <c r="H61" s="202"/>
-      <c r="I61" s="202"/>
-      <c r="J61" s="202"/>
-      <c r="K61" s="202"/>
-      <c r="L61" s="202"/>
-      <c r="M61" s="202"/>
-      <c r="N61" s="202"/>
-      <c r="O61" s="202"/>
-      <c r="P61" s="202"/>
+      <c r="A61" s="244"/>
+      <c r="B61" s="244"/>
+      <c r="C61" s="244"/>
+      <c r="D61" s="200"/>
+      <c r="E61" s="200"/>
+      <c r="F61" s="200"/>
+      <c r="G61" s="200"/>
+      <c r="H61" s="200"/>
+      <c r="I61" s="200"/>
+      <c r="J61" s="200"/>
+      <c r="K61" s="200"/>
+      <c r="L61" s="200"/>
+      <c r="M61" s="200"/>
+      <c r="N61" s="200"/>
+      <c r="O61" s="200"/>
+      <c r="P61" s="200"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5231,124 +5310,252 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="117" width="27.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="117" width="31.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="117" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="117" width="30.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="117" width="52.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="117" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="114" width="27.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="114" width="31.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="114" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="114" width="30.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="114" width="52.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="114" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="126" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="249" t="s">
+    <row r="1" s="123" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="247" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="249" t="s">
+      <c r="B1" s="247" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="249" t="s">
+      <c r="C1" s="247" t="s">
         <v>218</v>
       </c>
-      <c r="D1" s="249" t="s">
+      <c r="D1" s="247" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="249" t="s">
+      <c r="E1" s="247" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="250" t="s">
+      <c r="A2" s="248" t="s">
         <v>220</v>
       </c>
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="248" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="251" t="s">
+      <c r="C2" s="249" t="s">
         <v>222</v>
       </c>
-      <c r="D2" s="251"/>
-      <c r="E2" s="252" t="s">
+      <c r="D2" s="249"/>
+      <c r="E2" s="250" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="250" t="s">
+      <c r="A3" s="248" t="s">
         <v>224</v>
       </c>
-      <c r="B3" s="250" t="s">
+      <c r="B3" s="248" t="s">
         <v>225</v>
       </c>
-      <c r="C3" s="250"/>
-      <c r="D3" s="250"/>
-      <c r="E3" s="252" t="s">
+      <c r="C3" s="248"/>
+      <c r="D3" s="248"/>
+      <c r="E3" s="250" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="250" t="s">
+      <c r="A4" s="248" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="250" t="s">
+      <c r="B4" s="248" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="249" t="s">
         <v>229</v>
       </c>
-      <c r="D4" s="251" t="s">
+      <c r="D4" s="249" t="s">
         <v>230</v>
       </c>
-      <c r="E4" s="252" t="s">
+      <c r="E4" s="250" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="253" t="s">
+      <c r="A5" s="251" t="s">
         <v>232</v>
       </c>
-      <c r="B5" s="253" t="s">
+      <c r="B5" s="251" t="s">
         <v>233</v>
       </c>
-      <c r="C5" s="254" t="s">
+      <c r="C5" s="252" t="s">
         <v>234</v>
       </c>
-      <c r="D5" s="253"/>
-      <c r="E5" s="252" t="s">
+      <c r="D5" s="251"/>
+      <c r="E5" s="250" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="253" t="s">
+      <c r="A6" s="251" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="253"/>
-      <c r="C6" s="253"/>
-      <c r="D6" s="253"/>
-      <c r="E6" s="252" t="s">
+      <c r="B6" s="251"/>
+      <c r="C6" s="251"/>
+      <c r="D6" s="251"/>
+      <c r="E6" s="250" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="255" t="s">
+      <c r="A7" s="253" t="s">
         <v>238</v>
       </c>
-      <c r="B7" s="255"/>
-      <c r="C7" s="255"/>
-      <c r="D7" s="255"/>
-      <c r="E7" s="255" t="s">
+      <c r="B7" s="253"/>
+      <c r="C7" s="253"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="255" t="s">
+      <c r="A8" s="253" t="s">
         <v>240</v>
       </c>
-      <c r="B8" s="255"/>
-      <c r="C8" s="255"/>
-      <c r="D8" s="255"/>
-      <c r="E8" s="256" t="s">
+      <c r="B8" s="253"/>
+      <c r="C8" s="253"/>
+      <c r="D8" s="253"/>
+      <c r="E8" s="254" t="s">
         <v>241</v>
       </c>
     </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFDDDDDD"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="255" width="27.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="255" width="31.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="255" width="109.02"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="4" style="256" width="9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="9" style="256" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="256" width="9.34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="257" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="257" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="257" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="205.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="258" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="258" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="259" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="222.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="258" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="258" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" s="259" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="274" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="258" t="s">
+        <v>248</v>
+      </c>
+      <c r="B4" s="258" t="s">
+        <v>249</v>
+      </c>
+      <c r="C4" s="259" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="154.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="258" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="260" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="259" t="s">
+        <v>253</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFDDDDDD"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B1048576"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="255" width="27.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="255" width="109.02"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="3" style="256" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="0" width="9.34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="257" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="257" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="205.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="261" t="s">
+        <v>254</v>
+      </c>
+      <c r="B2" s="259" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5369,918 +5576,918 @@
   <dimension ref="A1:XFD1048576"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="55.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="104"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="28.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="36.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="28.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="66.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="33.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="26.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="28.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="14" width="36.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="36.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="26.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="17" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="18" width="32.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="18" width="5.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="18" width="18.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="18" width="5.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="18" width="22.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="18" width="5.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="18" width="25.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="18" width="5.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="18" width="41.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="18" width="5.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="18" width="43.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="29" min="26" style="18" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="39" min="30" style="19" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16352" min="40" style="18" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16359" min="16353" style="18" width="9.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16360" style="20" width="9.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="55.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="104"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="28.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="36.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="28.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="66.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="33.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="26.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="13" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="13" width="36.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="14" width="36.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="15" width="26.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="16" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="17" width="32.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="17" width="5.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="17" width="18.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="17" width="5.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="17" width="22.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="17" width="5.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="17" width="25.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="17" width="5.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="17" width="41.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="17" width="5.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="17" width="43.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="29" min="26" style="17" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="39" min="30" style="18" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16352" min="40" style="17" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16359" min="16353" style="17" width="9.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16360" style="19" width="9.37"/>
   </cols>
   <sheetData>
-    <row r="1" s="28" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="21" t="s">
+    <row r="1" s="27" customFormat="true" ht="20.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="M1" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="29"/>
-      <c r="AM1" s="29"/>
-      <c r="XEF1" s="20"/>
-      <c r="XEG1" s="20"/>
-      <c r="XEH1" s="20"/>
-      <c r="XEI1" s="20"/>
-      <c r="XEJ1" s="20"/>
-      <c r="XEK1" s="20"/>
-      <c r="XEL1" s="20"/>
-      <c r="XEM1" s="20"/>
-      <c r="XEN1" s="20"/>
-      <c r="XEO1" s="20"/>
-      <c r="XEP1" s="20"/>
-      <c r="XEQ1" s="20"/>
-      <c r="XER1" s="20"/>
-      <c r="XES1" s="20"/>
-      <c r="XET1" s="20"/>
-      <c r="XEU1" s="20"/>
-      <c r="XEV1" s="20"/>
-      <c r="XEW1" s="20"/>
-      <c r="XEX1" s="20"/>
-      <c r="XEY1" s="20"/>
-      <c r="XEZ1" s="20"/>
-      <c r="XFA1" s="20"/>
-      <c r="XFB1" s="20"/>
-      <c r="XFC1" s="20"/>
-      <c r="XFD1" s="20"/>
-    </row>
-    <row r="2" s="33" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="31"/>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-      <c r="AH2" s="19"/>
-      <c r="AI2" s="19"/>
-      <c r="AJ2" s="19"/>
-      <c r="AK2" s="19"/>
-      <c r="AL2" s="19"/>
-      <c r="AM2" s="19"/>
-      <c r="XEF2" s="20"/>
-      <c r="XEG2" s="20"/>
-      <c r="XEH2" s="20"/>
-      <c r="XEI2" s="20"/>
-      <c r="XEJ2" s="20"/>
-      <c r="XEK2" s="20"/>
-      <c r="XEL2" s="20"/>
-      <c r="XEM2" s="20"/>
-      <c r="XEN2" s="20"/>
-      <c r="XEO2" s="20"/>
-      <c r="XEP2" s="20"/>
-      <c r="XEQ2" s="20"/>
-      <c r="XER2" s="20"/>
-      <c r="XES2" s="20"/>
-      <c r="XET2" s="20"/>
-      <c r="XEU2" s="20"/>
-      <c r="XEV2" s="20"/>
-      <c r="XEW2" s="20"/>
-      <c r="XEX2" s="20"/>
-      <c r="XEY2" s="20"/>
-      <c r="XEZ2" s="20"/>
-      <c r="XFA2" s="20"/>
-      <c r="XFB2" s="20"/>
-      <c r="XFC2" s="20"/>
-      <c r="XFD2" s="20"/>
-    </row>
-    <row r="3" s="33" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="17"/>
-      <c r="AD3" s="19"/>
-      <c r="AE3" s="19"/>
-      <c r="AF3" s="19"/>
-      <c r="AG3" s="19"/>
-      <c r="AH3" s="19"/>
-      <c r="AI3" s="19"/>
-      <c r="AJ3" s="19"/>
-      <c r="AK3" s="19"/>
-      <c r="AL3" s="19"/>
-      <c r="AM3" s="19"/>
-      <c r="XEF3" s="20"/>
-      <c r="XEG3" s="20"/>
-      <c r="XEH3" s="20"/>
-      <c r="XEI3" s="20"/>
-      <c r="XEJ3" s="20"/>
-      <c r="XEK3" s="20"/>
-      <c r="XEL3" s="20"/>
-      <c r="XEM3" s="20"/>
-      <c r="XEN3" s="20"/>
-      <c r="XEO3" s="20"/>
-      <c r="XEP3" s="20"/>
-      <c r="XEQ3" s="20"/>
-      <c r="XER3" s="20"/>
-      <c r="XES3" s="20"/>
-      <c r="XET3" s="20"/>
-      <c r="XEU3" s="20"/>
-      <c r="XEV3" s="20"/>
-      <c r="XEW3" s="20"/>
-      <c r="XEX3" s="20"/>
-      <c r="XEY3" s="20"/>
-      <c r="XEZ3" s="20"/>
-      <c r="XFA3" s="20"/>
-      <c r="XFB3" s="20"/>
-      <c r="XFC3" s="20"/>
-      <c r="XFD3" s="20"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="XEF1" s="19"/>
+      <c r="XEG1" s="19"/>
+      <c r="XEH1" s="19"/>
+      <c r="XEI1" s="19"/>
+      <c r="XEJ1" s="19"/>
+      <c r="XEK1" s="19"/>
+      <c r="XEL1" s="19"/>
+      <c r="XEM1" s="19"/>
+      <c r="XEN1" s="19"/>
+      <c r="XEO1" s="19"/>
+      <c r="XEP1" s="19"/>
+      <c r="XEQ1" s="19"/>
+      <c r="XER1" s="19"/>
+      <c r="XES1" s="19"/>
+      <c r="XET1" s="19"/>
+      <c r="XEU1" s="19"/>
+      <c r="XEV1" s="19"/>
+      <c r="XEW1" s="19"/>
+      <c r="XEX1" s="19"/>
+      <c r="XEY1" s="19"/>
+      <c r="XEZ1" s="19"/>
+      <c r="XFA1" s="19"/>
+      <c r="XFB1" s="19"/>
+      <c r="XFC1" s="19"/>
+      <c r="XFD1" s="19"/>
+    </row>
+    <row r="2" s="32" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="30"/>
+      <c r="AD2" s="18"/>
+      <c r="AE2" s="18"/>
+      <c r="AF2" s="18"/>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18"/>
+      <c r="AK2" s="18"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="18"/>
+      <c r="XEF2" s="19"/>
+      <c r="XEG2" s="19"/>
+      <c r="XEH2" s="19"/>
+      <c r="XEI2" s="19"/>
+      <c r="XEJ2" s="19"/>
+      <c r="XEK2" s="19"/>
+      <c r="XEL2" s="19"/>
+      <c r="XEM2" s="19"/>
+      <c r="XEN2" s="19"/>
+      <c r="XEO2" s="19"/>
+      <c r="XEP2" s="19"/>
+      <c r="XEQ2" s="19"/>
+      <c r="XER2" s="19"/>
+      <c r="XES2" s="19"/>
+      <c r="XET2" s="19"/>
+      <c r="XEU2" s="19"/>
+      <c r="XEV2" s="19"/>
+      <c r="XEW2" s="19"/>
+      <c r="XEX2" s="19"/>
+      <c r="XEY2" s="19"/>
+      <c r="XEZ2" s="19"/>
+      <c r="XFA2" s="19"/>
+      <c r="XFB2" s="19"/>
+      <c r="XFC2" s="19"/>
+      <c r="XFD2" s="19"/>
+    </row>
+    <row r="3" s="32" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="16"/>
+      <c r="AD3" s="18"/>
+      <c r="AE3" s="18"/>
+      <c r="AF3" s="18"/>
+      <c r="AG3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18"/>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="18"/>
+      <c r="XEF3" s="19"/>
+      <c r="XEG3" s="19"/>
+      <c r="XEH3" s="19"/>
+      <c r="XEI3" s="19"/>
+      <c r="XEJ3" s="19"/>
+      <c r="XEK3" s="19"/>
+      <c r="XEL3" s="19"/>
+      <c r="XEM3" s="19"/>
+      <c r="XEN3" s="19"/>
+      <c r="XEO3" s="19"/>
+      <c r="XEP3" s="19"/>
+      <c r="XEQ3" s="19"/>
+      <c r="XER3" s="19"/>
+      <c r="XES3" s="19"/>
+      <c r="XET3" s="19"/>
+      <c r="XEU3" s="19"/>
+      <c r="XEV3" s="19"/>
+      <c r="XEW3" s="19"/>
+      <c r="XEX3" s="19"/>
+      <c r="XEY3" s="19"/>
+      <c r="XEZ3" s="19"/>
+      <c r="XFA3" s="19"/>
+      <c r="XFB3" s="19"/>
+      <c r="XFC3" s="19"/>
+      <c r="XFD3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="33"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="33"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="33"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="32"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="32"/>
+      <c r="Z7" s="32"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="33"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="33"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="33"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="32"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="33"/>
-      <c r="AC10" s="33"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="33"/>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="33"/>
-      <c r="Y11" s="33"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="33"/>
-      <c r="AC11" s="33"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="32"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="32"/>
+      <c r="Z11" s="32"/>
+      <c r="AA11" s="32"/>
+      <c r="AB11" s="32"/>
+      <c r="AC11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="33"/>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="33"/>
-      <c r="AC12" s="33"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="32"/>
+      <c r="W12" s="32"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="32"/>
+      <c r="Z12" s="32"/>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="32"/>
+      <c r="AC12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="33"/>
-      <c r="AC13" s="33"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="33"/>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="33"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="32"/>
+      <c r="Z14" s="32"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="32"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+      <c r="AA15" s="32"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="32"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="32"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="33"/>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="33"/>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="32"/>
+      <c r="AC17" s="32"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="33"/>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="33"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="32"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="32"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="33"/>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="33"/>
-      <c r="AB19" s="33"/>
-      <c r="AC19" s="33"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="32"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="33"/>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="33"/>
-      <c r="Y20" s="33"/>
-      <c r="Z20" s="33"/>
-      <c r="AA20" s="33"/>
-      <c r="AB20" s="33"/>
-      <c r="AC20" s="33"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="33"/>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="33"/>
-      <c r="Y21" s="33"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="33"/>
-      <c r="AB21" s="33"/>
-      <c r="AC21" s="33"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="33"/>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="33"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="33"/>
-      <c r="AB22" s="33"/>
-      <c r="AC22" s="33"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="32"/>
+      <c r="AB22" s="32"/>
+      <c r="AC22" s="32"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="33"/>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
-      <c r="Y23" s="33"/>
-      <c r="Z23" s="33"/>
-      <c r="AA23" s="33"/>
-      <c r="AB23" s="33"/>
-      <c r="AC23" s="33"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
+      <c r="AA23" s="32"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="32"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="33"/>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-      <c r="Z24" s="33"/>
-      <c r="AA24" s="33"/>
-      <c r="AB24" s="33"/>
-      <c r="AC24" s="33"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
+      <c r="AA24" s="32"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="33"/>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="33"/>
-      <c r="AA25" s="33"/>
-      <c r="AB25" s="33"/>
-      <c r="AC25" s="33"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
+      <c r="Z25" s="32"/>
+      <c r="AA25" s="32"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="32"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="33"/>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="33"/>
-      <c r="Y26" s="33"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="33"/>
-      <c r="AB26" s="33"/>
-      <c r="AC26" s="33"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="32"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="32"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="33"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="33"/>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="33"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="33"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="33"/>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="33"/>
-      <c r="Y28" s="33"/>
-      <c r="Z28" s="33"/>
-      <c r="AA28" s="33"/>
-      <c r="AB28" s="33"/>
-      <c r="AC28" s="33"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="33"/>
-      <c r="V29" s="33"/>
-      <c r="W29" s="33"/>
-      <c r="X29" s="33"/>
-      <c r="Y29" s="33"/>
-      <c r="Z29" s="33"/>
-      <c r="AA29" s="33"/>
-      <c r="AB29" s="33"/>
-      <c r="AC29" s="33"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="33"/>
-      <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="33"/>
-      <c r="Y30" s="33"/>
-      <c r="Z30" s="33"/>
-      <c r="AA30" s="33"/>
-      <c r="AB30" s="33"/>
-      <c r="AC30" s="33"/>
+      <c r="O30" s="32"/>
+      <c r="P30" s="32"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="32"/>
+      <c r="V30" s="32"/>
+      <c r="W30" s="32"/>
+      <c r="X30" s="32"/>
+      <c r="Y30" s="32"/>
+      <c r="Z30" s="32"/>
+      <c r="AA30" s="32"/>
+      <c r="AB30" s="32"/>
+      <c r="AC30" s="32"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="33"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="33"/>
-      <c r="V31" s="33"/>
-      <c r="W31" s="33"/>
-      <c r="X31" s="33"/>
-      <c r="Y31" s="33"/>
-      <c r="Z31" s="33"/>
-      <c r="AA31" s="33"/>
-      <c r="AB31" s="33"/>
-      <c r="AC31" s="33"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="32"/>
+      <c r="AA31" s="32"/>
+      <c r="AB31" s="32"/>
+      <c r="AC31" s="32"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O32" s="34"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="33"/>
-      <c r="S32" s="33"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="34"/>
-      <c r="W32" s="34"/>
-      <c r="X32" s="34"/>
-      <c r="Y32" s="34"/>
-      <c r="Z32" s="34"/>
-      <c r="AA32" s="34"/>
-      <c r="AB32" s="34"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="33"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="33"/>
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+      <c r="AA32" s="33"/>
+      <c r="AB32" s="33"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33"/>
-      <c r="U33" s="33"/>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="33"/>
-      <c r="Y33" s="33"/>
-      <c r="Z33" s="33"/>
-      <c r="AA33" s="33"/>
-      <c r="AB33" s="33"/>
-      <c r="AC33" s="33"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+      <c r="Z33" s="32"/>
+      <c r="AA33" s="32"/>
+      <c r="AB33" s="32"/>
+      <c r="AC33" s="32"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O34" s="34"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="34"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
-      <c r="AA34" s="34"/>
-      <c r="AB34" s="34"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="33"/>
+      <c r="U34" s="33"/>
+      <c r="V34" s="33"/>
+      <c r="W34" s="33"/>
+      <c r="X34" s="33"/>
+      <c r="Y34" s="33"/>
+      <c r="Z34" s="33"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O35" s="34"/>
-      <c r="P35" s="33"/>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="34"/>
-      <c r="W35" s="34"/>
-      <c r="X35" s="34"/>
-      <c r="Y35" s="34"/>
-      <c r="Z35" s="34"/>
-      <c r="AA35" s="34"/>
-      <c r="AB35" s="34"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="33"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="33"/>
+      <c r="Y35" s="33"/>
+      <c r="Z35" s="33"/>
+      <c r="AA35" s="33"/>
+      <c r="AB35" s="33"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O36" s="34"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33"/>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
-      <c r="AA36" s="34"/>
-      <c r="AB36" s="34"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="33"/>
+      <c r="U36" s="33"/>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="33"/>
+      <c r="Y36" s="33"/>
+      <c r="Z36" s="33"/>
+      <c r="AA36" s="33"/>
+      <c r="AB36" s="33"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O37" s="34"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="33"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="34"/>
-      <c r="W37" s="34"/>
-      <c r="X37" s="34"/>
-      <c r="Y37" s="34"/>
-      <c r="Z37" s="34"/>
-      <c r="AA37" s="34"/>
-      <c r="AB37" s="34"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="33"/>
+      <c r="U37" s="33"/>
+      <c r="V37" s="33"/>
+      <c r="W37" s="33"/>
+      <c r="X37" s="33"/>
+      <c r="Y37" s="33"/>
+      <c r="Z37" s="33"/>
+      <c r="AA37" s="33"/>
+      <c r="AB37" s="33"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O38" s="34"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33"/>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="34"/>
-      <c r="W38" s="34"/>
-      <c r="X38" s="34"/>
-      <c r="Y38" s="34"/>
-      <c r="Z38" s="34"/>
-      <c r="AA38" s="34"/>
-      <c r="AB38" s="34"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="33"/>
+      <c r="V38" s="33"/>
+      <c r="W38" s="33"/>
+      <c r="X38" s="33"/>
+      <c r="Y38" s="33"/>
+      <c r="Z38" s="33"/>
+      <c r="AA38" s="33"/>
+      <c r="AB38" s="33"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O39" s="34"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="W39" s="34"/>
-      <c r="X39" s="34"/>
-      <c r="Y39" s="34"/>
-      <c r="Z39" s="34"/>
-      <c r="AA39" s="34"/>
-      <c r="AB39" s="34"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="33"/>
+      <c r="V39" s="33"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="33"/>
+      <c r="Y39" s="33"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="35"/>
-      <c r="B73" s="35"/>
-      <c r="C73" s="35"/>
-      <c r="D73" s="35"/>
-      <c r="E73" s="35"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="38"/>
+      <c r="A73" s="34"/>
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="36"/>
+      <c r="L73" s="37"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="35"/>
-      <c r="B74" s="35"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37"/>
-      <c r="I74" s="37"/>
-      <c r="J74" s="37"/>
-      <c r="K74" s="37"/>
-      <c r="L74" s="38"/>
+      <c r="A74" s="34"/>
+      <c r="B74" s="34"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="34"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="37"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="35"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="35"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="36"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
-      <c r="L75" s="38"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36"/>
+      <c r="I75" s="36"/>
+      <c r="J75" s="36"/>
+      <c r="K75" s="36"/>
+      <c r="L75" s="37"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="35"/>
-      <c r="B76" s="35"/>
-      <c r="C76" s="35"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="36"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
-      <c r="J76" s="37"/>
-      <c r="K76" s="37"/>
-      <c r="L76" s="38"/>
+      <c r="A76" s="34"/>
+      <c r="B76" s="34"/>
+      <c r="C76" s="34"/>
+      <c r="D76" s="34"/>
+      <c r="E76" s="34"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="36"/>
+      <c r="K76" s="36"/>
+      <c r="L76" s="37"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="35"/>
-      <c r="B77" s="35"/>
-      <c r="C77" s="35"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="36"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37"/>
-      <c r="I77" s="37"/>
-      <c r="J77" s="37"/>
-      <c r="K77" s="37"/>
-      <c r="L77" s="38"/>
+      <c r="A77" s="34"/>
+      <c r="B77" s="34"/>
+      <c r="C77" s="34"/>
+      <c r="D77" s="34"/>
+      <c r="E77" s="34"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
+      <c r="I77" s="36"/>
+      <c r="J77" s="36"/>
+      <c r="K77" s="36"/>
+      <c r="L77" s="37"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="35"/>
-      <c r="B78" s="35"/>
-      <c r="C78" s="35"/>
-      <c r="D78" s="35"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
-      <c r="J78" s="37"/>
-      <c r="K78" s="37"/>
-      <c r="L78" s="38"/>
+      <c r="A78" s="34"/>
+      <c r="B78" s="34"/>
+      <c r="C78" s="34"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="34"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="36"/>
+      <c r="H78" s="36"/>
+      <c r="I78" s="36"/>
+      <c r="J78" s="36"/>
+      <c r="K78" s="36"/>
+      <c r="L78" s="37"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -6335,433 +6542,433 @@
   <dimension ref="A1:G64"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="39" width="40.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="39" width="26.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="39" width="147.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="39" width="42.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="39" width="43.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="53.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="17.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="8" style="20" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="19" width="9.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="38" width="40.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="38" width="26.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="38" width="147.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="38" width="42.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="38" width="43.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="18" width="53.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="17.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="8" style="19" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="18" width="9.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43" t="s">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="44"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="44"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="44"/>
-    </row>
-    <row r="5" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
+      <c r="E4" s="42"/>
+      <c r="F4" s="43"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="44"/>
-    </row>
-    <row r="6" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
+      <c r="E5" s="42"/>
+      <c r="F5" s="43"/>
+    </row>
+    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="44"/>
-    </row>
-    <row r="7" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
+      <c r="E6" s="42"/>
+      <c r="F6" s="43"/>
+    </row>
+    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="43"/>
-      <c r="F7" s="44"/>
-    </row>
-    <row r="8" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
+      <c r="E7" s="42"/>
+      <c r="F7" s="43"/>
+    </row>
+    <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="44"/>
-    </row>
-    <row r="9" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
+      <c r="E8" s="42"/>
+      <c r="F8" s="43"/>
+    </row>
+    <row r="9" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="44"/>
-    </row>
-    <row r="10" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
+      <c r="E9" s="42"/>
+      <c r="F9" s="43"/>
+    </row>
+    <row r="10" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="44"/>
-    </row>
-    <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="39" t="s">
+      <c r="E10" s="42"/>
+      <c r="F10" s="43"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="44"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="43"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="39" t="s">
+      <c r="A13" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="E13" s="43"/>
-      <c r="F13" s="44"/>
-    </row>
-    <row r="14" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="39" t="s">
+      <c r="E13" s="42"/>
+      <c r="F13" s="43"/>
+    </row>
+    <row r="14" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="47" t="s">
+      <c r="C14" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="43"/>
-      <c r="F14" s="44"/>
-    </row>
-    <row r="15" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="39" t="s">
+      <c r="E14" s="42"/>
+      <c r="F14" s="43"/>
+    </row>
+    <row r="15" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="44"/>
-    </row>
-    <row r="16" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="39" t="s">
+      <c r="E15" s="42"/>
+      <c r="F15" s="43"/>
+    </row>
+    <row r="16" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="43"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="43"/>
-      <c r="F17" s="44"/>
-    </row>
-    <row r="18" customFormat="false" ht="17.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
+      <c r="E17" s="42"/>
+      <c r="F17" s="43"/>
+    </row>
+    <row r="18" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C18" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="43"/>
-      <c r="F18" s="44"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="43"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="44"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="43"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="44"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="43"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="44"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="43"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="44"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="43"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="43"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="44"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="43"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="47"/>
+      <c r="C32" s="44"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="47"/>
+      <c r="C33" s="44"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="47"/>
+      <c r="C34" s="44"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="47"/>
+      <c r="C35" s="44"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="47"/>
+      <c r="C36" s="44"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="47"/>
+      <c r="C37" s="44"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="47"/>
+      <c r="C38" s="44"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="47"/>
+      <c r="C39" s="44"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="47"/>
+      <c r="C40" s="44"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="47"/>
+      <c r="C41" s="44"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C42" s="47"/>
+      <c r="C42" s="44"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="47"/>
+      <c r="C43" s="44"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="47"/>
+      <c r="C44" s="44"/>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="47"/>
+      <c r="C45" s="44"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="47"/>
+      <c r="C46" s="44"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="47"/>
+      <c r="C47" s="44"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="47"/>
+      <c r="C48" s="44"/>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="47"/>
+      <c r="C49" s="44"/>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="47"/>
+      <c r="C50" s="44"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="47"/>
+      <c r="C51" s="44"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="47"/>
+      <c r="C52" s="44"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="47"/>
+      <c r="C53" s="44"/>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="47"/>
+      <c r="C54" s="44"/>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="47"/>
+      <c r="C55" s="44"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="47"/>
+      <c r="C56" s="44"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="47"/>
+      <c r="C57" s="44"/>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C58" s="47"/>
+      <c r="C58" s="44"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="47"/>
+      <c r="C59" s="44"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="47"/>
+      <c r="C60" s="44"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="47"/>
+      <c r="C61" s="44"/>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="47"/>
+      <c r="C62" s="44"/>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="47"/>
+      <c r="C63" s="44"/>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="47"/>
+      <c r="C64" s="44"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -6776,11 +6983,11 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="D5" r:id="rId1" display="http://qudt.org/vocab/unit/PIXEL"/>
-    <hyperlink ref="D6" r:id="rId2" display="http://qudt.org/vocab/unit/MilliM"/>
+    <hyperlink ref="D6" r:id="rId2" display="http://qudt.org/vocab/unit/MilliM3"/>
     <hyperlink ref="D7" r:id="rId3" display="http://qudt.org/vocab/unit/ONE-PER-ONE"/>
     <hyperlink ref="D8" r:id="rId4" display="http://qudt.org/vocab/unit/MilliM"/>
     <hyperlink ref="D9" r:id="rId5" display="http://qudt.org/vocab/unit/GM"/>
-    <hyperlink ref="D10" r:id="rId6" display="http://qudt.org/vocab/unit/MilliM"/>
+    <hyperlink ref="D10" r:id="rId6" display="http://qudt.org/vocab/unit/MilliM2"/>
     <hyperlink ref="D14" r:id="rId7" display="http://qudt.org/vocab/unit/DAY"/>
     <hyperlink ref="D15" r:id="rId8" display="http://qudt.org/vocab/unit/MilliM-PER-DAY"/>
     <hyperlink ref="D16" r:id="rId9" display="http://qudt.org/vocab/unit/MilliL"/>
@@ -6805,209 +7012,209 @@
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="18" width="16.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="18" width="38.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="18" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="6" style="20" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="18" width="9.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="16.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="38.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="6" style="19" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="17" width="9.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="47" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="16"/>
+      <c r="E3" s="15"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="16"/>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16" t="s">
+      <c r="C8" s="15"/>
+      <c r="D8" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="16"/>
+      <c r="E8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16" t="s">
+      <c r="C9" s="15"/>
+      <c r="D9" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="15"/>
+      <c r="D10" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="51" t="s">
+      <c r="C11" s="15"/>
+      <c r="D11" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="16"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="51"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="48"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="C13" s="53"/>
-      <c r="D13" s="16" t="s">
+      <c r="C13" s="50"/>
+      <c r="D13" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7032,329 +7239,335 @@
   <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="18" width="10.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="18" width="12.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="41.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="18" width="20.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="69.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="18" width="21.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="43.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="18" width="10.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="54" width="37.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="10" style="19" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="18" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="55" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="18" width="9.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="10.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="12.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="41.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="20.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="69.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="21.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="43.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="17" width="10.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="51" width="37.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="10" style="18" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="17" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="52" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="17" width="9.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="56" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="60" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="57" t="s">
         <v>138</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="57" t="s">
         <v>139</v>
       </c>
-      <c r="F2" s="60"/>
-      <c r="G2" s="63" t="s">
+      <c r="F2" s="57"/>
+      <c r="G2" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="60"/>
-      <c r="I2" s="64" t="s">
+      <c r="H2" s="57"/>
+      <c r="I2" s="61" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="65" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="62" t="s">
         <v>143</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="57" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="66" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="63" t="s">
         <v>145</v>
       </c>
-      <c r="H3" s="60" t="s">
+      <c r="H3" s="57" t="s">
         <v>137</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="61" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" s="71" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="67" t="s">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="69" t="s">
+      <c r="C4" s="64"/>
+      <c r="D4" s="66" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67" t="s">
+      <c r="F4" s="64"/>
+      <c r="G4" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="67" t="s">
+      <c r="H4" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="I4" s="68" t="s">
+      <c r="I4" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
-      <c r="M4" s="70"/>
-      <c r="N4" s="70"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="73"/>
-    </row>
-    <row r="5" s="71" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="67" t="s">
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="70"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="65" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C5" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="66" t="s">
         <v>156</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67" t="s">
+      <c r="F5" s="64"/>
+      <c r="G5" s="64" t="s">
         <v>158</v>
       </c>
-      <c r="H5" s="67" t="s">
+      <c r="H5" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="I5" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="70"/>
-      <c r="N5" s="70"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="73"/>
-    </row>
-    <row r="6" s="71" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="67" t="s">
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="70"/>
+    </row>
+    <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="65" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="66" t="s">
         <v>163</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67" t="s">
+      <c r="F6" s="64"/>
+      <c r="G6" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="I6" s="68" t="s">
+      <c r="I6" s="65" t="s">
         <v>166</v>
       </c>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="73"/>
-    </row>
-    <row r="7" s="71" customFormat="true" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="67" t="s">
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="70"/>
+    </row>
+    <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="65" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="66" t="s">
         <v>170</v>
       </c>
-      <c r="E7" s="67" t="s">
+      <c r="E7" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="F7" s="67"/>
-      <c r="G7" s="67" t="s">
+      <c r="F7" s="64"/>
+      <c r="G7" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="H7" s="67" t="s">
+      <c r="H7" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="68" t="s">
+      <c r="I7" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="73"/>
-    </row>
-    <row r="8" s="71" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="67"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="73"/>
-    </row>
-    <row r="9" s="71" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="67"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="75"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="73"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="70"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="64"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
+      <c r="N8" s="67"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="69"/>
+      <c r="Q8" s="70"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="64"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="67"/>
+      <c r="N9" s="67"/>
+      <c r="O9" s="68"/>
+      <c r="P9" s="69"/>
+      <c r="Q9" s="70"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="60"/>
-      <c r="E10" s="60"/>
-      <c r="F10" s="60"/>
-      <c r="G10" s="60"/>
-      <c r="H10" s="60"/>
-      <c r="I10" s="64"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="61"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="64"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="61"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="64"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="61"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="60"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="64"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="61"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="60"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="64"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="61"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="64"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="61"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7395,26 +7608,26 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="76" width="16.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="76" width="42.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="76" width="29.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="20" width="9.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="73" width="16.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="73" width="42.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="73" width="29.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="19" width="9.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="C1" s="74" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7436,70 +7649,70 @@
   <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="18.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="84.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="18.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="20" width="26.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="19.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="20" width="24.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="20" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="18.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="84.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="18.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="26.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="19.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="24.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="19" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="85" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="79" t="s">
+    <row r="1" s="82" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="80" t="s">
+      <c r="B1" s="77" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="81" t="s">
+      <c r="C1" s="78" t="s">
         <v>176</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="E1" s="81" t="s">
+      <c r="E1" s="78" t="s">
         <v>178</v>
       </c>
-      <c r="F1" s="81" t="s">
+      <c r="F1" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="G1" s="83"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
     </row>
     <row r="2" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="86"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="93"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="92"/>
-      <c r="H3" s="92"/>
-      <c r="I3" s="92"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
+      <c r="I3" s="89"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="98"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="92"/>
+      <c r="A4" s="95"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="89"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -7521,211 +7734,211 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="20" width="32.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="53.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="20" width="45.88"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="20" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="19" width="32.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="53.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="45.88"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="19" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="104" customFormat="true" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="103" t="s">
+    <row r="1" s="101" customFormat="true" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="100" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="103" t="s">
+      <c r="C1" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="103" t="s">
+      <c r="D1" s="100" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="2" s="108" customFormat="true" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="105" t="s">
+    <row r="2" s="105" customFormat="true" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="102" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="C2" s="106" t="s">
+      <c r="C2" s="103" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="107" t="s">
+      <c r="D2" s="104" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="3" s="108" customFormat="true" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="109" t="s">
+    <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="106" t="s">
         <v>185</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="106" t="s">
         <v>186</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="C3" s="107" t="s">
         <v>187</v>
       </c>
-      <c r="D3" s="111" t="s">
+      <c r="D3" s="108" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="112" t="s">
+      <c r="A4" s="109" t="s">
         <v>189</v>
       </c>
-      <c r="B4" s="113" t="s">
+      <c r="B4" s="110" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="114" t="s">
+      <c r="C4" s="111" t="s">
         <v>191</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="D4" s="112" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="116"/>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
+      <c r="A5" s="113"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="116"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="116"/>
+      <c r="A6" s="113"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="116"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
-      <c r="D7" s="116"/>
+      <c r="A7" s="113"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="116"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="116"/>
+      <c r="A8" s="113"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="113"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="116"/>
-      <c r="B9" s="116"/>
-      <c r="C9" s="116"/>
-      <c r="D9" s="116"/>
+      <c r="A9" s="113"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="116"/>
-      <c r="B10" s="116"/>
-      <c r="C10" s="116"/>
-      <c r="D10" s="116"/>
+      <c r="A10" s="113"/>
+      <c r="B10" s="113"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
+      <c r="A11" s="113"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="116"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="116"/>
+      <c r="A12" s="113"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="116"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
+      <c r="A13" s="113"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="116"/>
-      <c r="B14" s="116"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="116"/>
+      <c r="A14" s="113"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="116"/>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
+      <c r="A15" s="113"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="116"/>
-      <c r="B16" s="116"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="116"/>
+      <c r="A16" s="113"/>
+      <c r="B16" s="113"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="116"/>
-      <c r="B17" s="116"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="116"/>
+      <c r="A17" s="113"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="116"/>
-      <c r="B18" s="116"/>
-      <c r="C18" s="116"/>
-      <c r="D18" s="116"/>
+      <c r="A18" s="113"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="116"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
+      <c r="A19" s="113"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="113"/>
+      <c r="D19" s="113"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="116"/>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
+      <c r="A20" s="113"/>
+      <c r="B20" s="113"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="113"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="116"/>
-      <c r="B21" s="116"/>
-      <c r="C21" s="116"/>
-      <c r="D21" s="116"/>
+      <c r="A21" s="113"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="116"/>
-      <c r="B22" s="116"/>
-      <c r="C22" s="116"/>
-      <c r="D22" s="116"/>
+      <c r="A22" s="113"/>
+      <c r="B22" s="113"/>
+      <c r="C22" s="113"/>
+      <c r="D22" s="113"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="116"/>
-      <c r="B23" s="116"/>
-      <c r="C23" s="116"/>
-      <c r="D23" s="116"/>
+      <c r="A23" s="113"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="113"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="116"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="116"/>
-      <c r="D24" s="116"/>
+      <c r="A24" s="113"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="113"/>
+      <c r="D24" s="113"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="116"/>
-      <c r="B25" s="116"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
+      <c r="A25" s="113"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="113"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="116"/>
-      <c r="B26" s="116"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="116"/>
+      <c r="A26" s="113"/>
+      <c r="B26" s="113"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="113"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="116"/>
-      <c r="B27" s="116"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
+      <c r="A27" s="113"/>
+      <c r="B27" s="113"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="113"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="116"/>
-      <c r="B28" s="116"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="116"/>
+      <c r="A28" s="113"/>
+      <c r="B28" s="113"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="113"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7752,360 +7965,360 @@
   <dimension ref="A1:BX18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="117" width="15.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="117" width="34.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="117" width="36.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="117" width="29.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="117" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="117" width="26.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="117" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="114" width="15.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="114" width="34.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="114" width="36.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="114" width="29.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="114" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="114" width="26.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="114" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="126" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="118" t="s">
+    <row r="1" s="123" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="119" t="s">
+      <c r="B1" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="C1" s="117" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="121" t="s">
+      <c r="D1" s="118" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="122" t="s">
+      <c r="E1" s="119" t="s">
         <v>177</v>
       </c>
-      <c r="F1" s="123" t="s">
+      <c r="F1" s="120" t="s">
         <v>178</v>
       </c>
-      <c r="G1" s="119" t="s">
+      <c r="G1" s="116" t="s">
         <v>179</v>
       </c>
-      <c r="H1" s="124"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="127"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
-      <c r="H2" s="133"/>
-      <c r="I2" s="133"/>
-      <c r="J2" s="133"/>
-      <c r="K2" s="133"/>
-      <c r="L2" s="133"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="134"/>
-      <c r="B3" s="135"/>
-      <c r="C3" s="136"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="141"/>
-      <c r="K3" s="141"/>
-      <c r="L3" s="141"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="132"/>
+      <c r="C3" s="133"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="135"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
     </row>
     <row r="4" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="142"/>
-      <c r="B4" s="143"/>
-      <c r="C4" s="144"/>
-      <c r="D4" s="144"/>
-      <c r="E4" s="145"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="148"/>
-      <c r="N4" s="148"/>
-      <c r="O4" s="148"/>
-      <c r="P4" s="148"/>
-      <c r="Q4" s="148"/>
-      <c r="R4" s="148"/>
-      <c r="S4" s="148"/>
-      <c r="T4" s="148"/>
-      <c r="U4" s="148"/>
-      <c r="V4" s="148"/>
-      <c r="W4" s="148"/>
-      <c r="X4" s="148"/>
-      <c r="Y4" s="148"/>
-      <c r="Z4" s="148"/>
-      <c r="AA4" s="148"/>
-      <c r="AB4" s="148"/>
-      <c r="AC4" s="148"/>
-      <c r="AD4" s="148"/>
-      <c r="AE4" s="148"/>
-      <c r="AF4" s="148"/>
-      <c r="AG4" s="148"/>
-      <c r="AH4" s="148"/>
-      <c r="AI4" s="148"/>
-      <c r="AJ4" s="148"/>
-      <c r="AK4" s="148"/>
-      <c r="AL4" s="148"/>
-      <c r="AM4" s="148"/>
-      <c r="AN4" s="148"/>
-      <c r="AO4" s="148"/>
-      <c r="AP4" s="148"/>
-      <c r="AQ4" s="148"/>
-      <c r="AR4" s="148"/>
-      <c r="AS4" s="148"/>
-      <c r="AT4" s="148"/>
-      <c r="AU4" s="148"/>
-      <c r="AV4" s="148"/>
-      <c r="AW4" s="148"/>
-      <c r="AX4" s="148"/>
-      <c r="AY4" s="148"/>
-      <c r="AZ4" s="148"/>
-      <c r="BA4" s="148"/>
-      <c r="BB4" s="148"/>
-      <c r="BC4" s="148"/>
-      <c r="BD4" s="148"/>
-      <c r="BE4" s="148"/>
-      <c r="BF4" s="148"/>
-      <c r="BG4" s="148"/>
-      <c r="BH4" s="148"/>
-      <c r="BI4" s="148"/>
-      <c r="BJ4" s="148"/>
-      <c r="BK4" s="148"/>
-      <c r="BL4" s="148"/>
-      <c r="BM4" s="148"/>
-      <c r="BN4" s="148"/>
-      <c r="BO4" s="148"/>
-      <c r="BP4" s="148"/>
-      <c r="BQ4" s="148"/>
-      <c r="BR4" s="148"/>
-      <c r="BS4" s="148"/>
-      <c r="BT4" s="148"/>
-      <c r="BU4" s="148"/>
-      <c r="BV4" s="148"/>
-      <c r="BW4" s="148"/>
-      <c r="BX4" s="148"/>
+      <c r="A4" s="139"/>
+      <c r="B4" s="140"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="144"/>
+      <c r="K4" s="144"/>
+      <c r="L4" s="144"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
+      <c r="O4" s="145"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="145"/>
+      <c r="R4" s="145"/>
+      <c r="S4" s="145"/>
+      <c r="T4" s="145"/>
+      <c r="U4" s="145"/>
+      <c r="V4" s="145"/>
+      <c r="W4" s="145"/>
+      <c r="X4" s="145"/>
+      <c r="Y4" s="145"/>
+      <c r="Z4" s="145"/>
+      <c r="AA4" s="145"/>
+      <c r="AB4" s="145"/>
+      <c r="AC4" s="145"/>
+      <c r="AD4" s="145"/>
+      <c r="AE4" s="145"/>
+      <c r="AF4" s="145"/>
+      <c r="AG4" s="145"/>
+      <c r="AH4" s="145"/>
+      <c r="AI4" s="145"/>
+      <c r="AJ4" s="145"/>
+      <c r="AK4" s="145"/>
+      <c r="AL4" s="145"/>
+      <c r="AM4" s="145"/>
+      <c r="AN4" s="145"/>
+      <c r="AO4" s="145"/>
+      <c r="AP4" s="145"/>
+      <c r="AQ4" s="145"/>
+      <c r="AR4" s="145"/>
+      <c r="AS4" s="145"/>
+      <c r="AT4" s="145"/>
+      <c r="AU4" s="145"/>
+      <c r="AV4" s="145"/>
+      <c r="AW4" s="145"/>
+      <c r="AX4" s="145"/>
+      <c r="AY4" s="145"/>
+      <c r="AZ4" s="145"/>
+      <c r="BA4" s="145"/>
+      <c r="BB4" s="145"/>
+      <c r="BC4" s="145"/>
+      <c r="BD4" s="145"/>
+      <c r="BE4" s="145"/>
+      <c r="BF4" s="145"/>
+      <c r="BG4" s="145"/>
+      <c r="BH4" s="145"/>
+      <c r="BI4" s="145"/>
+      <c r="BJ4" s="145"/>
+      <c r="BK4" s="145"/>
+      <c r="BL4" s="145"/>
+      <c r="BM4" s="145"/>
+      <c r="BN4" s="145"/>
+      <c r="BO4" s="145"/>
+      <c r="BP4" s="145"/>
+      <c r="BQ4" s="145"/>
+      <c r="BR4" s="145"/>
+      <c r="BS4" s="145"/>
+      <c r="BT4" s="145"/>
+      <c r="BU4" s="145"/>
+      <c r="BV4" s="145"/>
+      <c r="BW4" s="145"/>
+      <c r="BX4" s="145"/>
     </row>
     <row r="5" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="149"/>
-      <c r="B5" s="150"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="149"/>
-      <c r="H5" s="151"/>
-      <c r="I5" s="152"/>
-      <c r="J5" s="152"/>
-      <c r="K5" s="153"/>
-      <c r="L5" s="152"/>
-      <c r="M5" s="154"/>
-      <c r="N5" s="154"/>
-      <c r="O5" s="154"/>
-      <c r="P5" s="154"/>
-      <c r="Q5" s="154"/>
-      <c r="R5" s="154"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="156"/>
-      <c r="U5" s="156"/>
-      <c r="V5" s="156"/>
-      <c r="W5" s="156"/>
-      <c r="X5" s="156"/>
-      <c r="Y5" s="156"/>
-      <c r="Z5" s="156"/>
-      <c r="AA5" s="156"/>
-      <c r="AB5" s="156"/>
-      <c r="AC5" s="156"/>
-      <c r="AD5" s="156"/>
-      <c r="AE5" s="156"/>
-      <c r="AF5" s="156"/>
-      <c r="AG5" s="156"/>
-      <c r="AH5" s="156"/>
-      <c r="AI5" s="156"/>
-      <c r="AJ5" s="156"/>
-      <c r="AK5" s="156"/>
-      <c r="AL5" s="156"/>
-      <c r="AM5" s="156"/>
-      <c r="AN5" s="156"/>
-      <c r="AO5" s="156"/>
-      <c r="AP5" s="156"/>
-      <c r="AQ5" s="156"/>
-      <c r="AR5" s="156"/>
-      <c r="AS5" s="156"/>
-      <c r="AT5" s="156"/>
-      <c r="AU5" s="156"/>
-      <c r="AV5" s="156"/>
-      <c r="AW5" s="156"/>
-      <c r="AX5" s="156"/>
-      <c r="AY5" s="156"/>
-      <c r="AZ5" s="156"/>
-      <c r="BA5" s="156"/>
-      <c r="BB5" s="156"/>
-      <c r="BC5" s="156"/>
-      <c r="BD5" s="156"/>
-      <c r="BE5" s="156"/>
-      <c r="BF5" s="156"/>
-      <c r="BG5" s="156"/>
-      <c r="BH5" s="156"/>
-      <c r="BI5" s="156"/>
-      <c r="BJ5" s="156"/>
-      <c r="BK5" s="156"/>
-      <c r="BL5" s="156"/>
-      <c r="BM5" s="156"/>
-      <c r="BN5" s="156"/>
-      <c r="BO5" s="156"/>
-      <c r="BP5" s="156"/>
-      <c r="BQ5" s="156"/>
-      <c r="BR5" s="156"/>
-      <c r="BS5" s="156"/>
-      <c r="BT5" s="156"/>
-      <c r="BU5" s="156"/>
-      <c r="BV5" s="156"/>
-      <c r="BW5" s="156"/>
-      <c r="BX5" s="156"/>
+      <c r="A5" s="146"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="146"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="150"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="151"/>
+      <c r="N5" s="151"/>
+      <c r="O5" s="151"/>
+      <c r="P5" s="151"/>
+      <c r="Q5" s="151"/>
+      <c r="R5" s="151"/>
+      <c r="S5" s="152"/>
+      <c r="T5" s="153"/>
+      <c r="U5" s="153"/>
+      <c r="V5" s="153"/>
+      <c r="W5" s="153"/>
+      <c r="X5" s="153"/>
+      <c r="Y5" s="153"/>
+      <c r="Z5" s="153"/>
+      <c r="AA5" s="153"/>
+      <c r="AB5" s="153"/>
+      <c r="AC5" s="153"/>
+      <c r="AD5" s="153"/>
+      <c r="AE5" s="153"/>
+      <c r="AF5" s="153"/>
+      <c r="AG5" s="153"/>
+      <c r="AH5" s="153"/>
+      <c r="AI5" s="153"/>
+      <c r="AJ5" s="153"/>
+      <c r="AK5" s="153"/>
+      <c r="AL5" s="153"/>
+      <c r="AM5" s="153"/>
+      <c r="AN5" s="153"/>
+      <c r="AO5" s="153"/>
+      <c r="AP5" s="153"/>
+      <c r="AQ5" s="153"/>
+      <c r="AR5" s="153"/>
+      <c r="AS5" s="153"/>
+      <c r="AT5" s="153"/>
+      <c r="AU5" s="153"/>
+      <c r="AV5" s="153"/>
+      <c r="AW5" s="153"/>
+      <c r="AX5" s="153"/>
+      <c r="AY5" s="153"/>
+      <c r="AZ5" s="153"/>
+      <c r="BA5" s="153"/>
+      <c r="BB5" s="153"/>
+      <c r="BC5" s="153"/>
+      <c r="BD5" s="153"/>
+      <c r="BE5" s="153"/>
+      <c r="BF5" s="153"/>
+      <c r="BG5" s="153"/>
+      <c r="BH5" s="153"/>
+      <c r="BI5" s="153"/>
+      <c r="BJ5" s="153"/>
+      <c r="BK5" s="153"/>
+      <c r="BL5" s="153"/>
+      <c r="BM5" s="153"/>
+      <c r="BN5" s="153"/>
+      <c r="BO5" s="153"/>
+      <c r="BP5" s="153"/>
+      <c r="BQ5" s="153"/>
+      <c r="BR5" s="153"/>
+      <c r="BS5" s="153"/>
+      <c r="BT5" s="153"/>
+      <c r="BU5" s="153"/>
+      <c r="BV5" s="153"/>
+      <c r="BW5" s="153"/>
+      <c r="BX5" s="153"/>
     </row>
     <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="149"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="149"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="141"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="141"/>
-      <c r="L6" s="141"/>
-      <c r="U6" s="156"/>
-      <c r="V6" s="156"/>
-      <c r="W6" s="156"/>
-      <c r="X6" s="156"/>
-      <c r="Y6" s="156"/>
-      <c r="Z6" s="156"/>
-      <c r="AA6" s="156"/>
+      <c r="A6" s="146"/>
+      <c r="B6" s="154"/>
+      <c r="C6" s="146"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="138"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="U6" s="153"/>
+      <c r="V6" s="153"/>
+      <c r="W6" s="153"/>
+      <c r="X6" s="153"/>
+      <c r="Y6" s="153"/>
+      <c r="Z6" s="153"/>
+      <c r="AA6" s="153"/>
     </row>
     <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="149"/>
-      <c r="B7" s="158"/>
-      <c r="C7" s="149"/>
-      <c r="D7" s="149"/>
-      <c r="E7" s="149"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="149"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="141"/>
+      <c r="A7" s="146"/>
+      <c r="B7" s="155"/>
+      <c r="C7" s="146"/>
+      <c r="D7" s="146"/>
+      <c r="E7" s="146"/>
+      <c r="F7" s="146"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="159"/>
-      <c r="B8" s="159"/>
-      <c r="C8" s="159"/>
-      <c r="D8" s="159"/>
-      <c r="E8" s="159"/>
-      <c r="F8" s="159"/>
-      <c r="G8" s="159"/>
+      <c r="A8" s="156"/>
+      <c r="B8" s="156"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="156"/>
+      <c r="G8" s="156"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="159"/>
-      <c r="B9" s="159"/>
-      <c r="C9" s="159"/>
-      <c r="D9" s="159"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="159"/>
-      <c r="G9" s="159"/>
+      <c r="A9" s="156"/>
+      <c r="B9" s="156"/>
+      <c r="C9" s="156"/>
+      <c r="D9" s="156"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="159"/>
-      <c r="B10" s="159"/>
-      <c r="C10" s="159"/>
-      <c r="D10" s="159"/>
-      <c r="E10" s="159"/>
-      <c r="F10" s="159"/>
-      <c r="G10" s="159"/>
+      <c r="A10" s="156"/>
+      <c r="B10" s="156"/>
+      <c r="C10" s="156"/>
+      <c r="D10" s="156"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="156"/>
+      <c r="G10" s="156"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="159"/>
-      <c r="B11" s="159"/>
-      <c r="C11" s="159"/>
-      <c r="D11" s="159"/>
-      <c r="E11" s="159"/>
-      <c r="F11" s="159"/>
-      <c r="G11" s="159"/>
+      <c r="A11" s="156"/>
+      <c r="B11" s="156"/>
+      <c r="C11" s="156"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="156"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="159"/>
-      <c r="B12" s="159"/>
-      <c r="C12" s="159"/>
-      <c r="D12" s="159"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="159"/>
+      <c r="A12" s="156"/>
+      <c r="B12" s="156"/>
+      <c r="C12" s="156"/>
+      <c r="D12" s="156"/>
+      <c r="E12" s="156"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="156"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="159"/>
-      <c r="B13" s="159"/>
-      <c r="C13" s="159"/>
-      <c r="D13" s="159"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="159"/>
-      <c r="G13" s="159"/>
+      <c r="A13" s="156"/>
+      <c r="B13" s="156"/>
+      <c r="C13" s="156"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="156"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="159"/>
-      <c r="B14" s="159"/>
-      <c r="C14" s="159"/>
-      <c r="D14" s="159"/>
-      <c r="E14" s="159"/>
-      <c r="F14" s="159"/>
-      <c r="G14" s="159"/>
+      <c r="A14" s="156"/>
+      <c r="B14" s="156"/>
+      <c r="C14" s="156"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="156"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="156"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="159"/>
-      <c r="B15" s="159"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="159"/>
-      <c r="E15" s="159"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="159"/>
+      <c r="A15" s="156"/>
+      <c r="B15" s="156"/>
+      <c r="C15" s="156"/>
+      <c r="D15" s="156"/>
+      <c r="E15" s="156"/>
+      <c r="F15" s="156"/>
+      <c r="G15" s="156"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="159"/>
-      <c r="B16" s="159"/>
-      <c r="C16" s="159"/>
-      <c r="D16" s="159"/>
-      <c r="E16" s="159"/>
-      <c r="F16" s="159"/>
-      <c r="G16" s="159"/>
+      <c r="A16" s="156"/>
+      <c r="B16" s="156"/>
+      <c r="C16" s="156"/>
+      <c r="D16" s="156"/>
+      <c r="E16" s="156"/>
+      <c r="F16" s="156"/>
+      <c r="G16" s="156"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="159"/>
-      <c r="B17" s="159"/>
-      <c r="C17" s="159"/>
-      <c r="D17" s="159"/>
-      <c r="E17" s="159"/>
-      <c r="F17" s="159"/>
-      <c r="G17" s="159"/>
+      <c r="A17" s="156"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
+      <c r="F17" s="156"/>
+      <c r="G17" s="156"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="159"/>
-      <c r="B18" s="159"/>
-      <c r="C18" s="159"/>
-      <c r="D18" s="159"/>
-      <c r="E18" s="159"/>
-      <c r="F18" s="159"/>
-      <c r="G18" s="159"/>
+      <c r="A18" s="156"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="156"/>
+      <c r="E18" s="156"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="156"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
